--- a/xlsxFiles/Crossover_Cameos_in_Anime_Evidence_List_Only.xlsx
+++ b/xlsxFiles/Crossover_Cameos_in_Anime_Evidence_List_Only.xlsx
@@ -48382,804 +48382,805 @@
     <hyperlink ref="G899" r:id="rId1278" display="https://www.youtube.com/watch?v=trkcmVYr_gk"/>
     <hyperlink ref="E900" r:id="rId1279" display="Commercial - Mitsukoshi Children's Expo (1985)"/>
     <hyperlink ref="G900" r:id="rId1280" display="https://www.youtube.com/watch?v=trkcmVYr_gk"/>
-    <hyperlink ref="E902" r:id="rId1281" display="TV Episode 5"/>
-    <hyperlink ref="G902" r:id="rId1282" display="Hikaru can also be seen here."/>
-    <hyperlink ref="E903" r:id="rId1283" display="TV Episode 3"/>
-    <hyperlink ref="E904" r:id="rId1284" display="TV Episode 5"/>
-    <hyperlink ref="E905" r:id="rId1285" display="TV Episode 8"/>
-    <hyperlink ref="E906" r:id="rId1286" display="TV Episode 8"/>
-    <hyperlink ref="E907" r:id="rId1287" display="TV Episode 8 (1991)"/>
-    <hyperlink ref="G907" r:id="rId1288" display="He can also be seen here."/>
-    <hyperlink ref="E908" r:id="rId1289" display="TV Episode 49 (80s)"/>
-    <hyperlink ref="E909" r:id="rId1290" display="TV Episode 13"/>
-    <hyperlink ref="E910" r:id="rId1291" display="TV Episode 13"/>
-    <hyperlink ref="E911" r:id="rId1292" display="TV Episode 13"/>
-    <hyperlink ref="E912" r:id="rId1293" display="TV Episode 13"/>
-    <hyperlink ref="E913" r:id="rId1294" display="TV Episode 15"/>
-    <hyperlink ref="E914" r:id="rId1295" display="TV Episode 10"/>
-    <hyperlink ref="G914" r:id="rId1296" display="Monohoshi Dai can be seen here and Kawa Yui can again be seen here."/>
-    <hyperlink ref="E915" r:id="rId1297" display="TV Episode 10"/>
-    <hyperlink ref="E916" r:id="rId1298" display="TV Episode 110"/>
-    <hyperlink ref="E917" r:id="rId1299" display="TV Episode 5 (1983)"/>
-    <hyperlink ref="E918" r:id="rId1300" display="TV Episode 6 (1983)"/>
-    <hyperlink ref="E919" r:id="rId1301" display="TV Episode 6 (1983)"/>
-    <hyperlink ref="E920" r:id="rId1302" display="TV Episode 6 (1983)"/>
-    <hyperlink ref="E921" r:id="rId1303" display="TV Episode 8 (1983)"/>
-    <hyperlink ref="E922" r:id="rId1304" display="TV Episode 8 (1983)"/>
-    <hyperlink ref="E923" r:id="rId1305" display="TV Episode 111"/>
-    <hyperlink ref="E924" r:id="rId1306" display="TV Episode 118"/>
-    <hyperlink ref="E925" r:id="rId1307" display="TV Episode 23"/>
-    <hyperlink ref="E926" r:id="rId1308" display="TV Episode 23"/>
-    <hyperlink ref="G926" r:id="rId1309" display="You can see them more clear here."/>
-    <hyperlink ref="E927" r:id="rId1310" display="TV Episode 23"/>
-    <hyperlink ref="E928" r:id="rId1311" display="TV Episode 23"/>
-    <hyperlink ref="E929" r:id="rId1312" display="TV Episode 88"/>
-    <hyperlink ref="E930" r:id="rId1313" display="TV Episode 25"/>
-    <hyperlink ref="E931" r:id="rId1314" display="TV Episode 28"/>
-    <hyperlink ref="E932" r:id="rId1315" display="TV Episode 26"/>
-    <hyperlink ref="G932" r:id="rId1316" display="She also can be seen here and here."/>
-    <hyperlink ref="E933" r:id="rId1317" display="TV Episode 26"/>
-    <hyperlink ref="G933" r:id="rId1318" display="She has now a more dark blue hair instead of her usual blond hair. Altough the facial feature, with the hair style and ribbon is still the same. She also can be seen here, here and here."/>
-    <hyperlink ref="E934" r:id="rId1319" display="TV Episode 1"/>
-    <hyperlink ref="E935" r:id="rId1320" display="TV Episode 43 (Part 3)"/>
-    <hyperlink ref="E936" r:id="rId1321" display="TV Episode 98 (80s)"/>
-    <hyperlink ref="G936" r:id="rId1322" display="Yume can be seen here."/>
-    <hyperlink ref="E937" r:id="rId1323" display="TV Episode 39 (Part 3)"/>
-    <hyperlink ref="E938" r:id="rId1324" display="TV Episode 4 (Part 3)"/>
-    <hyperlink ref="G938" r:id="rId1325" display="As the character in the paiting/photograph is sentient, this count as a cameo"/>
-    <hyperlink ref="E939" r:id="rId1326" display="TV Episode 119 (80s)"/>
-    <hyperlink ref="G939" r:id="rId1327" display="A-ko can also be seen here."/>
-    <hyperlink ref="E940" r:id="rId1328" display="TV Episode 119 (80s)"/>
-    <hyperlink ref="E941" r:id="rId1329" display="TV Episode 17"/>
-    <hyperlink ref="E942" r:id="rId1330" display="TV Episode 19"/>
-    <hyperlink ref="E943" r:id="rId1331" display="TV Episode 21"/>
-    <hyperlink ref="G943" r:id="rId1332" display="She can also be seen here."/>
-    <hyperlink ref="E944" r:id="rId1333" display="TV Episode 114 (80s)"/>
-    <hyperlink ref="E945" r:id="rId1334" display="TV Episode 16"/>
-    <hyperlink ref="G945" r:id="rId1335" display="Megane can be seen here"/>
-    <hyperlink ref="E946" r:id="rId1336" display="TV Episode 145 (80s)"/>
-    <hyperlink ref="E947" r:id="rId1337" display="TV Episode 148 (80s)"/>
-    <hyperlink ref="G947" r:id="rId1338" display="Kyao can be seen here and Daiba with Gablae here."/>
-    <hyperlink ref="E948" r:id="rId1339" display="TV Episode 23"/>
-    <hyperlink ref="G948" r:id="rId1340" display="They can also be seen here."/>
-    <hyperlink ref="E949" r:id="rId1341" display="TV Episode 156 (80s)"/>
-    <hyperlink ref="G949" r:id="rId1342" display="This is level 2 as each of the characters move, like here for example. Chilthonia can be seen here."/>
-    <hyperlink ref="E950" r:id="rId1343" display="TV Episode 2"/>
-    <hyperlink ref="E951" r:id="rId1344" display="TV Episode 26"/>
-    <hyperlink ref="G951" r:id="rId1345" display="They can also be seen here."/>
-    <hyperlink ref="E952" r:id="rId1346" display="TV Episode 28"/>
-    <hyperlink ref="G952" r:id="rId1347" display="She can also be seen here, here, here and here."/>
-    <hyperlink ref="E953" r:id="rId1348" display="TV Episode 28"/>
-    <hyperlink ref="G953" r:id="rId1349" display="He can also be seen here"/>
-    <hyperlink ref="E954" r:id="rId1350" display="TV Episode 30"/>
-    <hyperlink ref="E955" r:id="rId1351" display="TV Episode 172 (80s)"/>
-    <hyperlink ref="E956" r:id="rId1352" display="TV Episode 15 (G)"/>
-    <hyperlink ref="G956" r:id="rId1353" display="The reason why this is on level 2 beside the multiple frames is that this boy is part of the plot of this episode"/>
-    <hyperlink ref="E957" r:id="rId1354" display="TV Episode 178 (80s)"/>
-    <hyperlink ref="E958" r:id="rId1355" display="TV Episode 178 (80s)"/>
-    <hyperlink ref="E959" r:id="rId1356" display="TV Episode 176 (80s)"/>
-    <hyperlink ref="E960" r:id="rId1357" display="TV Episode 85"/>
-    <hyperlink ref="G960" r:id="rId1358" display="They moved their eyes in later scenes"/>
-    <hyperlink ref="E961" r:id="rId1359" display="TV Episode 85"/>
-    <hyperlink ref="E962" r:id="rId1360" display="TV Episode 22"/>
-    <hyperlink ref="E963" r:id="rId1361" display="TV Episode 13 (Zeta)"/>
-    <hyperlink ref="E964" r:id="rId1362" display="TV Episode 177 (80s)"/>
-    <hyperlink ref="G964" r:id="rId1363" display="He is eating!"/>
-    <hyperlink ref="E965" r:id="rId1364" display="TV Episode 26"/>
-    <hyperlink ref="E966" r:id="rId1365" display="TV Episode 28"/>
-    <hyperlink ref="E967" r:id="rId1366" display="TV Episode 4"/>
-    <hyperlink ref="G967" r:id="rId1367" display="This, similar to Lum and Ataru in episode 26, Ganmo got edited out in later editions. Ayumi can also be seen here."/>
-    <hyperlink ref="E968" r:id="rId1368" display="Movie 1 - (1986)"/>
-    <hyperlink ref="E969" r:id="rId1369" display="Movie 1 - (1986)"/>
-    <hyperlink ref="E970" r:id="rId1370" display="Movie 1 - (1986)"/>
-    <hyperlink ref="E971" r:id="rId1371" display="Movie 1 - (1986)"/>
-    <hyperlink ref="E972" r:id="rId1372" display="TV Episode 20"/>
-    <hyperlink ref="E973" r:id="rId1373" display="Movie 3 - Remember My Love"/>
-    <hyperlink ref="E974" r:id="rId1374" display="Movie 3 - Remember My Love"/>
-    <hyperlink ref="E975" r:id="rId1375" display="Movie 3 - Remember My Love"/>
-    <hyperlink ref="G975" r:id="rId1376" display="Nurikabe design is specifically unique to the anime/manga show and Kitaro himsef is seen very briefly behind the legs of a women"/>
-    <hyperlink ref="E976" r:id="rId1377" display="Commercial - Partner Agent"/>
-    <hyperlink ref="E977" r:id="rId1378" display="Commercial - Partner Agent"/>
-    <hyperlink ref="E978" r:id="rId1379" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E979" r:id="rId1380" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E980" r:id="rId1381" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E981" r:id="rId1382" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E982" r:id="rId1383" display="TV Special - Black Jack: Karte NG Extras"/>
-    <hyperlink ref="E983" r:id="rId1384" display="Movie 4 - Lum The Forever"/>
-    <hyperlink ref="E984" r:id="rId1385" display="TV Special - Episode 12.5 (2008)"/>
-    <hyperlink ref="E985" r:id="rId1386" display="TV Episode 18"/>
-    <hyperlink ref="E986" r:id="rId1387" display="TV Episode 18"/>
-    <hyperlink ref="E987" r:id="rId1388" display="TV Episode 18"/>
-    <hyperlink ref="E988" r:id="rId1389" display="TV Episode 18"/>
-    <hyperlink ref="E989" r:id="rId1390" display="TV Special - Episode 12.5 (2008)"/>
-    <hyperlink ref="G989" r:id="rId1391" display="Dr. Nambu appears here."/>
-    <hyperlink ref="E990" r:id="rId1392" display="TV Special - Episode 12.5 (2008)"/>
-    <hyperlink ref="E991" r:id="rId1393" display="TV Special - Episode 12.5 (2008)"/>
-    <hyperlink ref="E992" r:id="rId1394" display="OVA - Elf 17"/>
-    <hyperlink ref="E993" r:id="rId1395" display="TV Episode 50 (Grendizer)"/>
-    <hyperlink ref="E994" r:id="rId1396" display="TV Episode 50 (Grendizer)"/>
-    <hyperlink ref="G994" r:id="rId1397" display="Seiji can also be seen here and here."/>
-    <hyperlink ref="E995" r:id="rId1398" display="TV Episode 50 (Grendizer)"/>
-    <hyperlink ref="G995" r:id="rId1399" display="He can also be seen here and here."/>
-    <hyperlink ref="E996" r:id="rId1400" display="TV Episode 3 (80s)"/>
-    <hyperlink ref="E997" r:id="rId1401" display="TV Episode 40"/>
-    <hyperlink ref="G997" r:id="rId1402" display="They are also seen here."/>
-    <hyperlink ref="E998" r:id="rId1403" display="TV Episode 38"/>
-    <hyperlink ref="E999" r:id="rId1404" display="TV Episode 38"/>
-    <hyperlink ref="E1000" r:id="rId1405" display="TV Episode 38"/>
-    <hyperlink ref="E1001" r:id="rId1406" display="TV Episode 38"/>
-    <hyperlink ref="E1002" r:id="rId1407" display="TV Episode 38"/>
-    <hyperlink ref="E1003" r:id="rId1408" display="OVA - (1991)"/>
-    <hyperlink ref="E1004" r:id="rId1409" display="OVA Episode 3 (Shin)"/>
-    <hyperlink ref="E1005" r:id="rId1410" display="OVA Episode 3 (Shin)"/>
-    <hyperlink ref="E1006" r:id="rId1411" display="OVA Episode 3 (Shin)"/>
-    <hyperlink ref="E1007" r:id="rId1412" display="Movie 1 - (1986)"/>
-    <hyperlink ref="E1008" r:id="rId1413" display="OVA Episode 2 (Shin)"/>
-    <hyperlink ref="E1009" r:id="rId1414" display="OVA Episode 2 (Shin)"/>
-    <hyperlink ref="G1009" r:id="rId1415" display="His face gets blowned up."/>
-    <hyperlink ref="E1010" r:id="rId1416" display="OVA Episode 8 (Shin)"/>
-    <hyperlink ref="E1011" r:id="rId1417" display="OVA Episode 8 (Shin)"/>
-    <hyperlink ref="E1012" r:id="rId1418" display="OVA - Elf 17"/>
-    <hyperlink ref="E1013" r:id="rId1419" display="TV Episode 24"/>
-    <hyperlink ref="E1014" r:id="rId1420" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="G1014" r:id="rId1421" display="Kuji can also be seen here and here."/>
-    <hyperlink ref="E1015" r:id="rId1422" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="G1015" r:id="rId1423" display="Ryo Asuka is in his manga design and be seen here and Mikki here."/>
-    <hyperlink ref="E1016" r:id="rId1424" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="G1016" r:id="rId1425" display="She can be seen here and here."/>
-    <hyperlink ref="E1017" r:id="rId1426" display="TV Episode 32"/>
-    <hyperlink ref="E1018" r:id="rId1427" display="TV Episode 21"/>
-    <hyperlink ref="E1019" r:id="rId1428" display="TV Episode 26"/>
-    <hyperlink ref="E1020" r:id="rId1429" display="OVA Episode 8 (Shin)"/>
-    <hyperlink ref="G1020" r:id="rId1430" display="Keiko can be seen here."/>
-    <hyperlink ref="E1021" r:id="rId1431" display="OVA Episode 8 (Shin)"/>
-    <hyperlink ref="E1022" r:id="rId1432" display="OVA Episode 4 (1991)"/>
-    <hyperlink ref="E1023" r:id="rId1433" display="TV Episode 27"/>
-    <hyperlink ref="E1024" r:id="rId1434" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="G1024" r:id="rId1435" display="He can also be seen here."/>
-    <hyperlink ref="E1025" r:id="rId1436" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="E1026" r:id="rId1437" display="OVA Episode 1 (1991)"/>
-    <hyperlink ref="G1026" r:id="rId1438" display="She can also be seen here."/>
-    <hyperlink ref="E1027" r:id="rId1439" display="OVA Episode 4 (1991)"/>
-    <hyperlink ref="G1027" r:id="rId1440" display="She can also be seen here and Alphone here."/>
-    <hyperlink ref="E1028" r:id="rId1441" display="TV Episode 1"/>
-    <hyperlink ref="E1029" r:id="rId1442" display="OVA - (1986)"/>
-    <hyperlink ref="G1029" r:id="rId1443" display="She is chearing"/>
-    <hyperlink ref="E1030" r:id="rId1444" display="OVA - (1986)"/>
-    <hyperlink ref="G1030" r:id="rId1445" display="They are chearing"/>
-    <hyperlink ref="E1031" r:id="rId1446" display="OVA - (1986)"/>
-    <hyperlink ref="G1031" r:id="rId1447" display="She is chearing and Hikaru can be seen here."/>
-    <hyperlink ref="E1032" r:id="rId1448" display="OVA - (1986)"/>
-    <hyperlink ref="G1032" r:id="rId1449" display="He is chearing and can also be seen here."/>
-    <hyperlink ref="E1033" r:id="rId1450" display="OVA - (1986)"/>
-    <hyperlink ref="G1033" r:id="rId1451" display="They are chearing and Gendou Kurosaki can be seen here and here."/>
-    <hyperlink ref="E1034" r:id="rId1452" display="OVA - (1986)"/>
-    <hyperlink ref="G1034" r:id="rId1453" display="They can also be seen here."/>
-    <hyperlink ref="E1035" r:id="rId1454" display="OVA - (1986)"/>
-    <hyperlink ref="G1035" r:id="rId1455" display="He is chearing."/>
-    <hyperlink ref="E1036" r:id="rId1456" display="Movie 3 - Cinderella Rhapsody"/>
-    <hyperlink ref="E1037" r:id="rId1457" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1038" r:id="rId1458" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1039" r:id="rId1459" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1040" r:id="rId1460" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1041" r:id="rId1461" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1042" r:id="rId1462" display="TV Special - Dora・Q・Perman"/>
-    <hyperlink ref="E1043" r:id="rId1463" display="TV Episode 148 (80s)"/>
-    <hyperlink ref="E1044" r:id="rId1464" display="TV Episode 46"/>
-    <hyperlink ref="E1045" r:id="rId1465" display="TV Episode 47"/>
-    <hyperlink ref="E1046" r:id="rId1466" display="Movie 1 - Panda Kopanda"/>
-    <hyperlink ref="G1046" r:id="rId1467" display="They can also be seen here."/>
-    <hyperlink ref="E1047" r:id="rId1468" display="Movie 1 - Panda Kopanda"/>
-    <hyperlink ref="E1048" r:id="rId1469" display="Movie 1 - Panda Kopanda"/>
-    <hyperlink ref="E1049" r:id="rId1470" display="OVA Episode 1 (1989)"/>
-    <hyperlink ref="E1050" r:id="rId1471" display="OVA Episode 2 (1989)"/>
-    <hyperlink ref="G1050" r:id="rId1472" display="This marks his first apperence with a voice, which VA will be used later in the 1991 OVA. He can be seen with Tosaka here."/>
-    <hyperlink ref="E1051" r:id="rId1473" display="Movie 4 - Lum The Forever"/>
-    <hyperlink ref="G1051" r:id="rId1474" display="Ta-Kun can be seen here."/>
-    <hyperlink ref="E1052" r:id="rId1475" display="TV Episode 34 (1966)"/>
-    <hyperlink ref="E1053" r:id="rId1476" display="OVA Episode 1"/>
-    <hyperlink ref="G1053" r:id="rId1477" display="He can also be seen here."/>
-    <hyperlink ref="E1054" r:id="rId1478" display="TV Episode 1"/>
-    <hyperlink ref="G1054" r:id="rId1479" display="Mako can be seen here."/>
-    <hyperlink ref="E1055" r:id="rId1480" display="TV Episode 1"/>
-    <hyperlink ref="E1056" r:id="rId1481" display="TV Episode 2"/>
-    <hyperlink ref="E1057" r:id="rId1482" display="TV Episode 2"/>
-    <hyperlink ref="E1058" r:id="rId1483" display="TV Episode 4"/>
-    <hyperlink ref="E1059" r:id="rId1484" display="TV Episode 6"/>
-    <hyperlink ref="G1059" r:id="rId1485" display="They can also be seen here."/>
-    <hyperlink ref="E1060" r:id="rId1486" display="TV Episode 6"/>
-    <hyperlink ref="E1061" r:id="rId1487" display="TV Episode 6"/>
-    <hyperlink ref="G1061" r:id="rId1488" display="He reacts can be seen here, here, here and here."/>
-    <hyperlink ref="E1062" r:id="rId1489" display="TV Episode 6"/>
-    <hyperlink ref="E1063" r:id="rId1490" display="TV Episode 6"/>
-    <hyperlink ref="E1064" r:id="rId1491" display="TV Episode 6"/>
-    <hyperlink ref="E1065" r:id="rId1492" display="TV Episode 1"/>
-    <hyperlink ref="E1066" r:id="rId1493" display="TV Episode 10"/>
-    <hyperlink ref="G1066" r:id="rId1494" display="He ran away."/>
-    <hyperlink ref="E1067" r:id="rId1495" display="TV Episode 13"/>
-    <hyperlink ref="E1068" r:id="rId1496" display="TV Episode 13"/>
-    <hyperlink ref="E1069" r:id="rId1497" display="TV Episode 13"/>
-    <hyperlink ref="E1070" r:id="rId1498" display="TV Episode 13"/>
-    <hyperlink ref="E1071" r:id="rId1499" display="TV Episode 14"/>
-    <hyperlink ref="G1071" r:id="rId1500" display="He appears here, here and here."/>
-    <hyperlink ref="E1072" r:id="rId1501" display="TV Episode 16"/>
-    <hyperlink ref="E1073" r:id="rId1502" display="TV Episode 21"/>
-    <hyperlink ref="E1074" r:id="rId1503" display="TV Episode 21"/>
-    <hyperlink ref="E1075" r:id="rId1504" display="TV Episode 100 (Part 2)"/>
-    <hyperlink ref="E1076" r:id="rId1505" display="TV Special - Star of the Giants vs. Mighty Atom"/>
-    <hyperlink ref="E1077" r:id="rId1506" display="TV Special - Star of the Giants vs. Mighty Atom"/>
-    <hyperlink ref="E1078" r:id="rId1507" display="TV Episode 21 (OG)"/>
-    <hyperlink ref="E1079" r:id="rId1508" display="Movie - (1983)"/>
-    <hyperlink ref="G1079" r:id="rId1509" display="This has ALOT of Gundam references and cameos. Haro is shown regularly through out the movie, not only that but Char can also seen here up close."/>
-    <hyperlink ref="E1080" r:id="rId1510" display="TV Episode 71 (1983)"/>
-    <hyperlink ref="E1081" r:id="rId1511" display="TV Episode 21 (1983)"/>
-    <hyperlink ref="E1082" r:id="rId1512" display="TV Episode 21 (1983)"/>
-    <hyperlink ref="E1083" r:id="rId1513" display="TV Episode 21 (1983)"/>
-    <hyperlink ref="E1084" r:id="rId1514" display="TV Episode 21 (1983)"/>
-    <hyperlink ref="G1084" r:id="rId1515" display="The untouched Italian version reveals the side brows that confirms its Lupin. Nobuhiro OKASAKO has worked both in Captain Tsubasa and Lupin."/>
-    <hyperlink ref="E1085" r:id="rId1516" display="TV Episode 21 (Season 2)"/>
-    <hyperlink ref="E1086" r:id="rId1517" display="OVA - Devilman: The Birth (1987)"/>
-    <hyperlink ref="E1087" r:id="rId1518" display="TV Episode 50 (Season 2)"/>
-    <hyperlink ref="G1087" r:id="rId1519" display="They look very adult like."/>
-    <hyperlink ref="E1088" r:id="rId1520" display="TV Episode 88 (1980)"/>
-    <hyperlink ref="E1089" r:id="rId1521" display="TV Episode 226 (1980)"/>
-    <hyperlink ref="E1090" r:id="rId1522" display="TV Episode 226 (1980)"/>
-    <hyperlink ref="E1091" r:id="rId1523" display="TV Episode 226 (1980)"/>
-    <hyperlink ref="E1092" r:id="rId1524" display="TV Episode 226 (1980)"/>
-    <hyperlink ref="E1093" r:id="rId1525" display="OVA Episode 2 (Shin)"/>
-    <hyperlink ref="E1094" r:id="rId1526" display="TV Episode 19 (Season 1)"/>
-    <hyperlink ref="E1095" r:id="rId1527" display="TV Episode 19 (Season 1)"/>
-    <hyperlink ref="E1096" r:id="rId1528" display="TV Episode 19 (Season 1)"/>
-    <hyperlink ref="E1097" r:id="rId1529" display="TV Episode 1 (Season 1)"/>
-    <hyperlink ref="G1097" r:id="rId1530" display="She also is seen here and here."/>
-    <hyperlink ref="E1098" r:id="rId1531" display="TV Episode 10 (Season 2)"/>
-    <hyperlink ref="E1099" r:id="rId1532" display="TV Episode 10 (Season 4)"/>
-    <hyperlink ref="G1099" r:id="rId1533" display="Yep, its her alright."/>
-    <hyperlink ref="E1100" r:id="rId1534" display="TV Episode 18"/>
-    <hyperlink ref="G1100" r:id="rId1535" display="As this may be a dream, this still consider as they exists on the same plane. Its also seen here and here."/>
-    <hyperlink ref="E1101" r:id="rId1536" display="TV Episode 18"/>
-    <hyperlink ref="G1101" r:id="rId1537" display="As this may be a dream, this still consider as they exists on the same plane. Its also seen here and here."/>
-    <hyperlink ref="E1102" r:id="rId1538" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1102" r:id="rId1539" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1103" r:id="rId1540" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1103" r:id="rId1541" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1104" r:id="rId1542" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1104" r:id="rId1543" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1105" r:id="rId1544" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1105" r:id="rId1545" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1106" r:id="rId1546" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1106" r:id="rId1547" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1107" r:id="rId1548" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1107" r:id="rId1549" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1108" r:id="rId1550" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1108" r:id="rId1551" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1109" r:id="rId1552" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1109" r:id="rId1553" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1110" r:id="rId1554" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1110" r:id="rId1555" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1111" r:id="rId1556" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1111" r:id="rId1557" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1112" r:id="rId1558" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1112" r:id="rId1559" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1113" r:id="rId1560" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1113" r:id="rId1561" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1114" r:id="rId1562" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1114" r:id="rId1563" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1115" r:id="rId1564" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
-    <hyperlink ref="G1115" r:id="rId1565" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
-    <hyperlink ref="E1116" r:id="rId1566" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1116" r:id="rId1567" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1117" r:id="rId1568" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1117" r:id="rId1569" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1118" r:id="rId1570" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1118" r:id="rId1571" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1119" r:id="rId1572" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1119" r:id="rId1573" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1120" r:id="rId1574" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1120" r:id="rId1575" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1121" r:id="rId1576" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1121" r:id="rId1577" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1122" r:id="rId1578" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1122" r:id="rId1579" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1123" r:id="rId1580" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1123" r:id="rId1581" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1124" r:id="rId1582" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1124" r:id="rId1583" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1125" r:id="rId1584" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1125" r:id="rId1585" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1126" r:id="rId1586" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1126" r:id="rId1587" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1127" r:id="rId1588" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
-    <hyperlink ref="G1127" r:id="rId1589" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
-    <hyperlink ref="E1128" r:id="rId1590" display="TV Episode 2"/>
-    <hyperlink ref="E1129" r:id="rId1591" display="TV Episode 2"/>
-    <hyperlink ref="E1130" r:id="rId1592" display="TV Episode 2"/>
-    <hyperlink ref="E1131" r:id="rId1593" display="Movie 3 - The Legend of the Gold of Babylon"/>
-    <hyperlink ref="E1132" r:id="rId1594" display="Movie 3 - The Legend of the Gold of Babylon"/>
-    <hyperlink ref="E1133" r:id="rId1595" display="TV Episode 1"/>
-    <hyperlink ref="E1134" r:id="rId1596" display="TV Episode 44 (80s)"/>
-    <hyperlink ref="G1134" r:id="rId1597" display="Since the manga was out during this episode premier , Hibaris color is more after the manga appearance. She also is seen here."/>
-    <hyperlink ref="E1135" r:id="rId1598" display="Movie 5 - Dead or Alive"/>
-    <hyperlink ref="E1136" r:id="rId1599" display="Movie 5 - Dead or Alive"/>
-    <hyperlink ref="E1137" r:id="rId1600" display="Movie 5 - Dead or Alive"/>
-    <hyperlink ref="E1138" r:id="rId1601" display="Movie 5 - Dead or Alive"/>
-    <hyperlink ref="E1139" r:id="rId1602" display="Movie 5 - Dead or Alive"/>
-    <hyperlink ref="E1140" r:id="rId1603" display="TV Episode 6 (OG)"/>
-    <hyperlink ref="E1141" r:id="rId1604" display="TV Episode 4"/>
-    <hyperlink ref="G1141" r:id="rId1605" display="The Fossil Creature appears here and here."/>
-    <hyperlink ref="E1142" r:id="rId1606" display="TV Episode 4"/>
-    <hyperlink ref="E1143" r:id="rId1607" display="TV Episode 15"/>
-    <hyperlink ref="E1144" r:id="rId1608" display="TV Episode 15"/>
-    <hyperlink ref="E1145" r:id="rId1609" display="TV Episode 15"/>
-    <hyperlink ref="E1146" r:id="rId1610" display="TV Episode 15"/>
-    <hyperlink ref="G1146" r:id="rId1611" display="Godai can be seen here and here."/>
-    <hyperlink ref="E1147" r:id="rId1612" display="TV Episode 15"/>
-    <hyperlink ref="E1148" r:id="rId1613" display="TV Episode 15"/>
-    <hyperlink ref="E1149" r:id="rId1614" display="TV Episode 16"/>
-    <hyperlink ref="G1149" r:id="rId1615" display="Max and Milia can be seen here and here"/>
-    <hyperlink ref="E1150" r:id="rId1616" display="TV Episode 16"/>
-    <hyperlink ref="G1150" r:id="rId1617" display="She runs."/>
-    <hyperlink ref="E1151" r:id="rId1618" display="TV Episode 16"/>
-    <hyperlink ref="E1152" r:id="rId1619" display="TV Episode 10"/>
-    <hyperlink ref="E1153" r:id="rId1620" display="TV Episode 5"/>
-    <hyperlink ref="G1153" r:id="rId1621" display="They appear constantly in this episode. Boss's little sister can be seen here."/>
-    <hyperlink ref="E1154" r:id="rId1622" display="TV Episode 37"/>
-    <hyperlink ref="E1155" r:id="rId1623" display="TV Episode 2 (Yatterman 2008)"/>
-    <hyperlink ref="E1156" r:id="rId1624" display="TV Episode 7 (Yatterman 2008)"/>
-    <hyperlink ref="E1157" r:id="rId1625" display="TV Episode 24 (Yatterman 2008)"/>
-    <hyperlink ref="G1157" r:id="rId1626" display="Jinpei, Ryu, Ken and Joe can be seen here and they smile."/>
-    <hyperlink ref="E1158" r:id="rId1627" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1159" r:id="rId1628" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1160" r:id="rId1629" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="G1160" r:id="rId1630" display="The car gets trashed later on."/>
-    <hyperlink ref="E1161" r:id="rId1631" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1162" r:id="rId1632" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1163" r:id="rId1633" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1164" r:id="rId1634" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1165" r:id="rId1635" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1166" r:id="rId1636" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1167" r:id="rId1637" display="OVA - Time Bokan: Royal Revival"/>
-    <hyperlink ref="E1168" r:id="rId1638" display="TV Episode 25 (Yatterman 2008)"/>
-    <hyperlink ref="G1168" r:id="rId1639" display="Ryu appears here and here."/>
-    <hyperlink ref="E1169" r:id="rId1640" display="TV Episode 10"/>
-    <hyperlink ref="E1170" r:id="rId1641" display="TV Episode 12"/>
-    <hyperlink ref="E1171" r:id="rId1642" display="TV Episode 13"/>
-    <hyperlink ref="E1172" r:id="rId1643" display="TV Episode 17"/>
-    <hyperlink ref="E1173" r:id="rId1644" display="ONA Episode 5"/>
-    <hyperlink ref="E1174" r:id="rId1645" display="TV Episode 44 (Season 1)"/>
-    <hyperlink ref="E1175" r:id="rId1646" display="TV Episode 5 (Unlimited Psychic Squad)"/>
-    <hyperlink ref="E1176" r:id="rId1647" display="OVA - 2008"/>
-    <hyperlink ref="E1177" r:id="rId1648" display="OVA Episode 2 (Goku)"/>
-    <hyperlink ref="E1178" r:id="rId1649" display="Special - Hetalia = Fantasia"/>
-    <hyperlink ref="E1179" r:id="rId1650" display="Special Event - Anime Tenchou x Touhou Project"/>
-    <hyperlink ref="E1180" r:id="rId1651" display="Special Event - Anime Tenchou x Touhou Project"/>
-    <hyperlink ref="E1181" r:id="rId1652" display="Movie - Lupin III vs. Cat's Eye"/>
-    <hyperlink ref="E1182" r:id="rId1653" display="Movie - Lupin III vs. Cat's Eye"/>
-    <hyperlink ref="E1183" r:id="rId1654" display="TV Episode 13"/>
-    <hyperlink ref="E1184" r:id="rId1655" display="TV Episode 13"/>
-    <hyperlink ref="E1185" r:id="rId1656" display="TV Episode 14"/>
-    <hyperlink ref="E1186" r:id="rId1657" display="TV Episode 14"/>
-    <hyperlink ref="E1187" r:id="rId1658" display="TV Episode 71"/>
-    <hyperlink ref="E1188" r:id="rId1659" display="TV Episode 30"/>
-    <hyperlink ref="E1189" r:id="rId1660" display="TV Episode 3 (Season 2)"/>
-    <hyperlink ref="E1190" r:id="rId1661" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1191" r:id="rId1662" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1192" r:id="rId1663" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1193" r:id="rId1664" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1194" r:id="rId1665" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1195" r:id="rId1666" display="Commercial - Inuyasha Manga Trailer (1996)"/>
-    <hyperlink ref="E1196" r:id="rId1667" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1197" r:id="rId1668" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1198" r:id="rId1669" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1199" r:id="rId1670" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1200" r:id="rId1671" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1201" r:id="rId1672" display="Commercial - Detective Conan Manga Commercial (1995)"/>
-    <hyperlink ref="E1202" r:id="rId1673" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
-    <hyperlink ref="E1203" r:id="rId1674" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
-    <hyperlink ref="E1204" r:id="rId1675" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
-    <hyperlink ref="E1205" r:id="rId1676" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
-    <hyperlink ref="E1206" r:id="rId1677" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1207" r:id="rId1678" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1208" r:id="rId1679" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1209" r:id="rId1680" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1210" r:id="rId1681" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1211" r:id="rId1682" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
-    <hyperlink ref="E1212" r:id="rId1683" display="Commercial - LOVe Manga Trailer (1996)"/>
-    <hyperlink ref="E1213" r:id="rId1684" display="Commercial - LOVe Manga Trailer (1996)"/>
-    <hyperlink ref="E1214" r:id="rId1685" display="Commercial - LOVe Manga Trailer (1996)"/>
-    <hyperlink ref="E1215" r:id="rId1686" display="Commercial - LOVe Manga Trailer (1996)"/>
-    <hyperlink ref="E1216" r:id="rId1687" display="TV Episode 3"/>
-    <hyperlink ref="E1217" r:id="rId1688" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1218" r:id="rId1689" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1219" r:id="rId1690" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1220" r:id="rId1691" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1221" r:id="rId1692" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1222" r:id="rId1693" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1223" r:id="rId1694" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1224" r:id="rId1695" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
-    <hyperlink ref="E1225" r:id="rId1696" display="Commercial - H2 Manga Commercial (1996)"/>
-    <hyperlink ref="E1226" r:id="rId1697" display="Commercial - H2 Manga Commercial (1996)"/>
-    <hyperlink ref="E1227" r:id="rId1698" display="Commercial - H2 Manga Commercial (1996)"/>
-    <hyperlink ref="E1228" r:id="rId1699" display="Commercial - H2 Manga Commercial (1996)"/>
-    <hyperlink ref="E1229" r:id="rId1700" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="G1229" r:id="rId1701" display="Genma can be seen here."/>
-    <hyperlink ref="E1230" r:id="rId1702" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="E1231" r:id="rId1703" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="E1232" r:id="rId1704" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="E1233" r:id="rId1705" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="E1234" r:id="rId1706" display="Commercial - Major Manga Commercial (1995)"/>
-    <hyperlink ref="E1235" r:id="rId1707" display="TV Episode 15"/>
-    <hyperlink ref="E1236" r:id="rId1708" display="TV Episode 37"/>
-    <hyperlink ref="G1236" r:id="rId1709" display="They also appear here and here."/>
-    <hyperlink ref="E1237" r:id="rId1710" display="TV Episode 30 (1980)"/>
-    <hyperlink ref="E1238" r:id="rId1711" display="TV Episode 30 (1980)"/>
-    <hyperlink ref="E1239" r:id="rId1712" display="TV Episode 3 (1969)"/>
-    <hyperlink ref="E1240" r:id="rId1713" display="TV Episode 25 (Part 6)"/>
-    <hyperlink ref="E1241" r:id="rId1714" display="TV Episode 25 (Part 6)"/>
-    <hyperlink ref="E1242" r:id="rId1715" display="TV Episode 25 (Part 6)"/>
-    <hyperlink ref="E1243" r:id="rId1716" display="TV Episode 26 (Part 6)"/>
-    <hyperlink ref="G1243" r:id="rId1717" display="Only mentioned through broadcasting channel but does techincally coexist in the world temporarily."/>
-    <hyperlink ref="E1244" r:id="rId1718" display="TV Episode 16"/>
-    <hyperlink ref="E1245" r:id="rId1719" display="TV Episode 22"/>
-    <hyperlink ref="G1245" r:id="rId1720" display="Nobita and the gang can be seen here."/>
-    <hyperlink ref="E1246" r:id="rId1721" display="TV Episode 5 (Lupin Zero)"/>
-    <hyperlink ref="E1247" r:id="rId1722" display="TV Episode 48"/>
-    <hyperlink ref="E1248" r:id="rId1723" display="TV Episode 48"/>
-    <hyperlink ref="E1249" r:id="rId1724" display="TV Episode 49"/>
-    <hyperlink ref="G1249" r:id="rId1725" display="They can be seen here."/>
-    <hyperlink ref="E1250" r:id="rId1726" display="TV Episode 49"/>
-    <hyperlink ref="E1251" r:id="rId1727" display="TV Episode 49"/>
-    <hyperlink ref="E1252" r:id="rId1728" display="TV Episode 49"/>
-    <hyperlink ref="G1252" r:id="rId1729" display="Ittan Mome can be seen here."/>
-    <hyperlink ref="E1253" r:id="rId1730" display="TV Episode 49"/>
-    <hyperlink ref="E1254" r:id="rId1731" display="TV Episode 49"/>
-    <hyperlink ref="G1254" r:id="rId1732" display="He can be seen here and here."/>
-    <hyperlink ref="E1255" r:id="rId1733" display="TV Episode 49"/>
-    <hyperlink ref="E1256" r:id="rId1734" display="TV Episode 49"/>
-    <hyperlink ref="E1257" r:id="rId1735" display="TV Episode 49"/>
-    <hyperlink ref="G1257" r:id="rId1736" display="He can also be seen here."/>
-    <hyperlink ref="E1258" r:id="rId1737" display="Movie - 1970"/>
-    <hyperlink ref="E1259" r:id="rId1738" display="TV Episode 47"/>
-    <hyperlink ref="E1260" r:id="rId1739" display="TV Episode 45"/>
-    <hyperlink ref="G1260" r:id="rId1740" display="He can also be seen here."/>
-    <hyperlink ref="E1261" r:id="rId1741" display="TV Episode 45"/>
-    <hyperlink ref="E1262" r:id="rId1742" display="TV Episode 45"/>
-    <hyperlink ref="E1263" r:id="rId1743" display="TV Episode 44"/>
-    <hyperlink ref="E1264" r:id="rId1744" display="TV Episode 44"/>
-    <hyperlink ref="E1265" r:id="rId1745" display="TV Episode 10"/>
-    <hyperlink ref="E1266" r:id="rId1746" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
-    <hyperlink ref="E1267" r:id="rId1747" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
-    <hyperlink ref="E1268" r:id="rId1748" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
-    <hyperlink ref="E1269" r:id="rId1749" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
-    <hyperlink ref="E1270" r:id="rId1750" display="TV Episode 37"/>
-    <hyperlink ref="E1271" r:id="rId1751" display="TV Episode 37"/>
-    <hyperlink ref="E1272" r:id="rId1752" display="TV Episode 37"/>
-    <hyperlink ref="G1272" r:id="rId1753" display="He can also be seen here."/>
-    <hyperlink ref="E1273" r:id="rId1754" display="TV Episode 37"/>
-    <hyperlink ref="G1273" r:id="rId1755" display="Kogenta Sarutobi can be seen here and here."/>
-    <hyperlink ref="E1274" r:id="rId1756" display="TV Episode 33"/>
-    <hyperlink ref="E1275" r:id="rId1757" display="TV Episode 27"/>
-    <hyperlink ref="G1275" r:id="rId1758" display="Ataru can be seen here. Funny how this is from Hanpeita fantasy as he and Ryuunosuke share the same VA"/>
-    <hyperlink ref="E1276" r:id="rId1759" display="TV Episode 27"/>
-    <hyperlink ref="G1276" r:id="rId1760" display="He can also be seen here."/>
-    <hyperlink ref="E1277" r:id="rId1761" display="TV Episode 27"/>
-    <hyperlink ref="E1278" r:id="rId1762" display="TV Episode 27"/>
-    <hyperlink ref="E1279" r:id="rId1763" display="TV Episode 20"/>
-    <hyperlink ref="G1279" r:id="rId1764" display="Mako can also be seen here."/>
-    <hyperlink ref="E1280" r:id="rId1765" display="TV Episode 20"/>
-    <hyperlink ref="G1280" r:id="rId1766" display="He is also seen here, here, here and here."/>
-    <hyperlink ref="E1281" r:id="rId1767" display="TV Episode 38"/>
-    <hyperlink ref="E1282" r:id="rId1768" display="Movie - Lupin III vs. Cat's Eye"/>
-    <hyperlink ref="E1283" r:id="rId1769" display="Movie - Lupin III vs. Cat's Eye"/>
-    <hyperlink ref="E1284" r:id="rId1770" display="TV Special - Special 3 (OG)"/>
-    <hyperlink ref="E1285" r:id="rId1771" display="TV Episode 1 (OG)"/>
-    <hyperlink ref="E1286" r:id="rId1772" display="Movie - Gu Gu Ganmo (1985)"/>
-    <hyperlink ref="G1286" r:id="rId1773" display="It can also be seen here."/>
-    <hyperlink ref="E1287" r:id="rId1774" display="TV Episode 18"/>
-    <hyperlink ref="E1288" r:id="rId1775" display="Commercial - H2 Manga Commercial (1996)"/>
-    <hyperlink ref="E1289" r:id="rId1776" display="TV Episode 52 (1980)"/>
-    <hyperlink ref="E1290" r:id="rId1777" display="TV Episode 52 (1980)"/>
-    <hyperlink ref="E1291" r:id="rId1778" display="TV Episode 52 (1980)"/>
-    <hyperlink ref="E1292" r:id="rId1779" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1293" r:id="rId1780" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1294" r:id="rId1781" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1295" r:id="rId1782" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1296" r:id="rId1783" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1297" r:id="rId1784" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1298" r:id="rId1785" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1299" r:id="rId1786" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1300" r:id="rId1787" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1301" r:id="rId1788" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1302" r:id="rId1789" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1303" r:id="rId1790" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1304" r:id="rId1791" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1305" r:id="rId1792" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1306" r:id="rId1793" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1307" r:id="rId1794" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1308" r:id="rId1795" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
-    <hyperlink ref="E1309" r:id="rId1796" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
-    <hyperlink ref="E1310" r:id="rId1797" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
-    <hyperlink ref="E1311" r:id="rId1798" display="TV Episode 35 (Stream)"/>
-    <hyperlink ref="G1311" r:id="rId1799" display="B-ko and C-ko as well"/>
-    <hyperlink ref="E1312" r:id="rId1800" display="TV Episode 3 (OG)"/>
-    <hyperlink ref="E1313" r:id="rId1801" display="TV Episode 137 (80s)"/>
-    <hyperlink ref="G1313" r:id="rId1802" display="They also appears here, here, here, here, here and here."/>
-    <hyperlink ref="E1314" r:id="rId1803" display="TV Episode 137 (80s)"/>
-    <hyperlink ref="G1314" r:id="rId1804" display="They are also seen here."/>
-    <hyperlink ref="E1315" r:id="rId1805" display="TV Episode 22 (20s)"/>
-    <hyperlink ref="E1316" r:id="rId1806" display="TV Episode 158 (80s)"/>
-    <hyperlink ref="E1317" r:id="rId1807" display="TV Episode 3"/>
-    <hyperlink ref="G1317" r:id="rId1808" display="She gasps."/>
-    <hyperlink ref="E1318" r:id="rId1809" display="TV Episode 3"/>
-    <hyperlink ref="E1319" r:id="rId1810" display="TV Episode 8 (1982)"/>
-    <hyperlink ref="E1320" r:id="rId1811" display="TV Episode 5 (1982)"/>
-    <hyperlink ref="E1321" r:id="rId1812" display="TV Episode 2"/>
-    <hyperlink ref="E1322" r:id="rId1813" display="TV Episode 30"/>
-    <hyperlink ref="G1322" r:id="rId1814" display="Arthur Rank can be seen here."/>
-    <hyperlink ref="E1323" r:id="rId1815" display="TV Episode 30"/>
-    <hyperlink ref="E1324" r:id="rId1816" display="TV Episode 30"/>
-    <hyperlink ref="E1325" r:id="rId1817" display="TV Episode 9 (OG)"/>
-    <hyperlink ref="E1326" r:id="rId1818" display="TV Episode 8 (OG)"/>
-    <hyperlink ref="E1327" r:id="rId1819" display="TV Episode 9 (OG)"/>
-    <hyperlink ref="E1328" r:id="rId1820" display="OVA - Farewell My Lovely + Pentagona Dolls"/>
-    <hyperlink ref="E1329" r:id="rId1821" display="TV Episode 13"/>
-    <hyperlink ref="E1330" r:id="rId1822" display="TV Episode 13"/>
-    <hyperlink ref="E1331" r:id="rId1823" display="TV Episode 5"/>
-    <hyperlink ref="E1332" r:id="rId1824" display="TV Episode 50"/>
-    <hyperlink ref="E1333" r:id="rId1825" display="TV Episode 50"/>
-    <hyperlink ref="E1334" r:id="rId1826" display="TV Episode 50"/>
-    <hyperlink ref="E1335" r:id="rId1827" display="TV Episode 50"/>
-    <hyperlink ref="E1336" r:id="rId1828" display="TV Episode 19"/>
-    <hyperlink ref="E1337" r:id="rId1829" display="TV Episode 19"/>
-    <hyperlink ref="E1338" r:id="rId1830" display="TV Episode 19"/>
-    <hyperlink ref="E1339" r:id="rId1831" display="TV Episode 59"/>
-    <hyperlink ref="E1340" r:id="rId1832" display="TV Episode 42"/>
-    <hyperlink ref="E1341" r:id="rId1833" display="TV Episode 59"/>
-    <hyperlink ref="E1342" r:id="rId1834" display="TV Episode 49"/>
-    <hyperlink ref="E1343" r:id="rId1835" display="TV Episode 39 (0079)"/>
-    <hyperlink ref="E1344" r:id="rId1836" display="TV Episode 8"/>
-    <hyperlink ref="E1345" r:id="rId1837" display="TV Episode 8"/>
-    <hyperlink ref="E1346" r:id="rId1838" display="TV Episode 8"/>
-    <hyperlink ref="E1347" r:id="rId1839" display="TV Episode 20 (OG)"/>
-    <hyperlink ref="E1348" r:id="rId1840" display="TV Episode 11"/>
-    <hyperlink ref="E1349" r:id="rId1841" display="TV Episode 11"/>
-    <hyperlink ref="E1350" r:id="rId1842" display="TV Episode 13"/>
-    <hyperlink ref="E1351" r:id="rId1843" display="TV Episode 13"/>
-    <hyperlink ref="E1352" r:id="rId1844" display="TV Episode 13"/>
-    <hyperlink ref="E1353" r:id="rId1845" display="TV Episode 13"/>
-    <hyperlink ref="E1354" r:id="rId1846" display="TV Episode 182"/>
-    <hyperlink ref="E1355" r:id="rId1847" display="TV Episode 26"/>
-    <hyperlink ref="E1356" r:id="rId1848" display="TV Episode 10"/>
-    <hyperlink ref="G1356" r:id="rId1849" display="He is arroused."/>
-    <hyperlink ref="E1357" r:id="rId1850" display="TV Episode 19"/>
-    <hyperlink ref="E1358" r:id="rId1851" display="TV Episode 19"/>
-    <hyperlink ref="E1359" r:id="rId1852" display="TV Episode 19"/>
-    <hyperlink ref="E1360" r:id="rId1853" display="TV Episode 19"/>
-    <hyperlink ref="E1361" r:id="rId1854" display="TV Episode 23"/>
-    <hyperlink ref="G1361" r:id="rId1855" display="He also appears here."/>
-    <hyperlink ref="E1362" r:id="rId1856" display="TV Episode 23"/>
-    <hyperlink ref="E1363" r:id="rId1857" display="TV Episode 23"/>
-    <hyperlink ref="G1363" r:id="rId1858" display="He also appears here thanks to the animation cel and zoomed."/>
-    <hyperlink ref="E1364" r:id="rId1859" display="TV Episode 23"/>
-    <hyperlink ref="E1365" r:id="rId1860" display="TV Episode 19"/>
-    <hyperlink ref="E1366" r:id="rId1861" display="TV Episode 31"/>
-    <hyperlink ref="E1367" r:id="rId1862" display="TV Episode 32"/>
-    <hyperlink ref="G1367" r:id="rId1863" display="She also appears here."/>
-    <hyperlink ref="E1368" r:id="rId1864" display="TV Episode 32"/>
-    <hyperlink ref="G1368" r:id="rId1865" display="She also appears here."/>
-    <hyperlink ref="E1369" r:id="rId1866" display="TV Episode 32"/>
-    <hyperlink ref="G1369" r:id="rId1867" display="She also appears here."/>
-    <hyperlink ref="E1370" r:id="rId1868" display="TV Episode 32"/>
-    <hyperlink ref="E1371" r:id="rId1869" display="TV Episode 36"/>
-    <hyperlink ref="E1372" r:id="rId1870" display="TV Episode 36"/>
-    <hyperlink ref="E1373" r:id="rId1871" display="TV Episode 36"/>
-    <hyperlink ref="E1374" r:id="rId1872" display="TV Episode 36"/>
-    <hyperlink ref="E1375" r:id="rId1873" display="TV Episode 36"/>
-    <hyperlink ref="E1376" r:id="rId1874" display="TV Episode 36"/>
-    <hyperlink ref="G1376" r:id="rId1875" display="This is reused from episode 23. He also appears here thanks to the animation cel and zoomed."/>
-    <hyperlink ref="E1377" r:id="rId1876" display="TV Episode 36"/>
-    <hyperlink ref="E1378" r:id="rId1877" display="TV Episode 36"/>
-    <hyperlink ref="G1378" r:id="rId1878" display="This is reused from episode 23. You can see them more clear here."/>
-    <hyperlink ref="E1379" r:id="rId1879" display="TV Episode 12"/>
-    <hyperlink ref="E1380" r:id="rId1880" display="TV Episode 13"/>
-    <hyperlink ref="E1381" r:id="rId1881" display="TV Episode 15"/>
-    <hyperlink ref="E1382" r:id="rId1882" display="TV Episode 18"/>
-    <hyperlink ref="E1383" r:id="rId1883" display="TV Episode 18"/>
-    <hyperlink ref="E1384" r:id="rId1884" display="TV Episode 18"/>
-    <hyperlink ref="E1385" r:id="rId1885" display="TV Episode 1"/>
-    <hyperlink ref="E1386" r:id="rId1886" display="TV Episode 181 (80s)"/>
-    <hyperlink ref="E1387" r:id="rId1887" display="TV Episode 181 (80s)"/>
-    <hyperlink ref="E1388" r:id="rId1888" display="TV Episode 19"/>
-    <hyperlink ref="E1389" r:id="rId1889" display="TV Episode 3"/>
-    <hyperlink ref="E1390" r:id="rId1890" display="TV Episode 3"/>
-    <hyperlink ref="E1391" r:id="rId1891" display="TV Episode 3"/>
-    <hyperlink ref="E1392" r:id="rId1892" display="TV Episode 4"/>
-    <hyperlink ref="E1393" r:id="rId1893" display="TV Episode 4"/>
-    <hyperlink ref="E1394" r:id="rId1894" display="TV Episode 4"/>
-    <hyperlink ref="E1395" r:id="rId1895" display="TV Episode 4"/>
-    <hyperlink ref="E1396" r:id="rId1896" display="TV Episode 4"/>
-    <hyperlink ref="G1396" r:id="rId1897" display="She also appears here."/>
-    <hyperlink ref="E1397" r:id="rId1898" display="TV Episode 9"/>
-    <hyperlink ref="E1398" r:id="rId1899" display="TV Episode 10"/>
-    <hyperlink ref="E1399" r:id="rId1900" display="TV Episode 10"/>
-    <hyperlink ref="E1400" r:id="rId1901" display="TV Episode 10"/>
-    <hyperlink ref="E1401" r:id="rId1902" display="TV Episode 25 (OG)"/>
-    <hyperlink ref="E1402" r:id="rId1903" display="TV Episode 12"/>
-    <hyperlink ref="E1403" r:id="rId1904" display="TV Episode 12"/>
-    <hyperlink ref="E1404" r:id="rId1905" display="TV Episode 21 (Z)"/>
-    <hyperlink ref="E1405" r:id="rId1906" display="TV Episode 20 (Z)"/>
-    <hyperlink ref="E1406" r:id="rId1907" display="TV Episode 30 (OG)"/>
-    <hyperlink ref="E1407" r:id="rId1908" display="TV Episode 86 (OG)"/>
-    <hyperlink ref="E1408" r:id="rId1909" display="TV Episode 107 (OG)"/>
-    <hyperlink ref="E1409" r:id="rId1910" display="TV Episode 109 (OG)"/>
-    <hyperlink ref="E1410" r:id="rId1911" display="TV Episode 14"/>
-    <hyperlink ref="E1411" r:id="rId1912" display="TV Episode 14"/>
-    <hyperlink ref="E1412" r:id="rId1913" display="TV Episode 16"/>
-    <hyperlink ref="E1413" r:id="rId1914" display="TV Episode 18"/>
-    <hyperlink ref="E1414" r:id="rId1915" display="Movie - Angel Dust"/>
-    <hyperlink ref="E1415" r:id="rId1916" display="TV Episode 9"/>
-    <hyperlink ref="E1416" r:id="rId1917" display="Special - Tokyo Crisis"/>
-    <hyperlink ref="E1417" r:id="rId1918" display="Movie - Ribbon no Kishi"/>
-    <hyperlink ref="E1418" r:id="rId1919" display="Movie - Ribbon no Kishi"/>
-    <hyperlink ref="E1419" r:id="rId1920" display="TV Episode 1"/>
-    <hyperlink ref="E1420" r:id="rId1921" display="TV Episode 14 (OG)"/>
-    <hyperlink ref="G1420" r:id="rId1922" display="She gets blown away."/>
-    <hyperlink ref="E1421" r:id="rId1923" display="TV Episode 15 (OG)"/>
-    <hyperlink ref="E1422" r:id="rId1924" display="TV Episode 15 (OG)"/>
-    <hyperlink ref="E1423" r:id="rId1925" display="TV Episode 15 (OG)"/>
-    <hyperlink ref="E1424" r:id="rId1926" display="TV Episode 23 (OG)"/>
-    <hyperlink ref="E1425" r:id="rId1927" display="TV Episode 18 (OG)"/>
-    <hyperlink ref="E1426" r:id="rId1928" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="E1427" r:id="rId1929" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="G1427" r:id="rId1930" display="Kate can also be seen here, Barts here and Luchina here."/>
-    <hyperlink ref="E1428" r:id="rId1931" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="E1429" r:id="rId1932" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="E1430" r:id="rId1933" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="E1431" r:id="rId1934" display="TV Episode 26 (OG)"/>
-    <hyperlink ref="E1432" r:id="rId1935" display="TV Episode 23 (OG)"/>
-    <hyperlink ref="E1433" r:id="rId1936" display="Movie 4 - Lum The Forever"/>
-    <hyperlink ref="E1434" r:id="rId1937" display="TV Episode 31 (OG)"/>
-    <hyperlink ref="E1435" r:id="rId1938" display="TV Episode 34 (OG)"/>
-    <hyperlink ref="G1435" r:id="rId1939" display="It can also be seen here and here."/>
-    <hyperlink ref="E1436" r:id="rId1940" display="TV Episode 34 (OG)"/>
-    <hyperlink ref="E1437" r:id="rId1941" display="TV Episode 35 (OG)"/>
-    <hyperlink ref="G1437" r:id="rId1942" display="It can also be seen here."/>
-    <hyperlink ref="E1438" r:id="rId1943" display="TV Episode 35 (OG)"/>
-    <hyperlink ref="E1439" r:id="rId1944" display="OVA Episode 2"/>
-    <hyperlink ref="E1440" r:id="rId1945" display="TV Episode 34 (OG)"/>
-    <hyperlink ref="E1441" r:id="rId1946" display="OVA Episode 5 (Macross II)"/>
-    <hyperlink ref="E1442" r:id="rId1947" display="Movie - Black Jack: Dr. Pinoko's Adventure"/>
-    <hyperlink ref="E1443" r:id="rId1948" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1444" r:id="rId1949" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1445" r:id="rId1950" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1446" r:id="rId1951" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1447" r:id="rId1952" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1448" r:id="rId1953" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1449" r:id="rId1954" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1450" r:id="rId1955" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1451" r:id="rId1956" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1452" r:id="rId1957" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1453" r:id="rId1958" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1454" r:id="rId1959" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1455" r:id="rId1960" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1456" r:id="rId1961" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1457" r:id="rId1962" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1458" r:id="rId1963" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1459" r:id="rId1964" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1460" r:id="rId1965" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1461" r:id="rId1966" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1462" r:id="rId1967" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1463" r:id="rId1968" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1464" r:id="rId1969" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1465" r:id="rId1970" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1466" r:id="rId1971" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1467" r:id="rId1972" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1468" r:id="rId1973" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1469" r:id="rId1974" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1470" r:id="rId1975" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1471" r:id="rId1976" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1472" r:id="rId1977" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1473" r:id="rId1978" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1474" r:id="rId1979" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1475" r:id="rId1980" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1476" r:id="rId1981" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1477" r:id="rId1982" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1478" r:id="rId1983" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1479" r:id="rId1984" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1480" r:id="rId1985" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1481" r:id="rId1986" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1482" r:id="rId1987" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1483" r:id="rId1988" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1484" r:id="rId1989" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1485" r:id="rId1990" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1486" r:id="rId1991" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1487" r:id="rId1992" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1488" r:id="rId1993" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1489" r:id="rId1994" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1490" r:id="rId1995" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1491" r:id="rId1996" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1492" r:id="rId1997" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1493" r:id="rId1998" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1494" r:id="rId1999" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1495" r:id="rId2000" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1496" r:id="rId2001" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1497" r:id="rId2002" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1498" r:id="rId2003" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1499" r:id="rId2004" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1500" r:id="rId2005" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1501" r:id="rId2006" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1502" r:id="rId2007" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1503" r:id="rId2008" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1504" r:id="rId2009" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1505" r:id="rId2010" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1506" r:id="rId2011" display="OVA - Ravex in Tezuka World"/>
-    <hyperlink ref="E1507" r:id="rId2012" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1508" r:id="rId2013" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1509" r:id="rId2014" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1510" r:id="rId2015" display="TV Special - Last Miracle 20th Century"/>
-    <hyperlink ref="E1511" r:id="rId2016" display="OVA Episode 3 (Mobile Suit SD Gundam)"/>
-    <hyperlink ref="E1512" r:id="rId2017" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1513" r:id="rId2018" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1514" r:id="rId2019" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1515" r:id="rId2020" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1516" r:id="rId2021" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1517" r:id="rId2022" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1518" r:id="rId2023" display="Movie - Choro-Q Dougram"/>
-    <hyperlink ref="E1519" r:id="rId2024" display="TV Episode 18 (Zeta)"/>
-    <hyperlink ref="E1520" r:id="rId2025" display="Movie - (1983)"/>
-    <hyperlink ref="E1521" r:id="rId2026" display="ONA - Genjitsu no Rimuru: Sunshine in the Slime"/>
-    <hyperlink ref="E1522" r:id="rId2027" display="ONA - Genjitsu no Rimuru: Sunshine in the Slime"/>
-    <hyperlink ref="E1523" r:id="rId2028" display="TV Episode 3 (OG)"/>
-    <hyperlink ref="E1524" r:id="rId2029" display="TV Episode 11 (OG)"/>
-    <hyperlink ref="G1524" r:id="rId2030" display="She also appears here."/>
-    <hyperlink ref="E1525" r:id="rId2031" display="TV Episode 12 (OG)"/>
-    <hyperlink ref="G1525" r:id="rId2032" display="They can also be seen here."/>
-    <hyperlink ref="E1526" r:id="rId2033" display="TV Episode 16 (OG)"/>
-    <hyperlink ref="E1527" r:id="rId2034" display="TV Episode 21 (OG)"/>
-    <hyperlink ref="E1528" r:id="rId2035" display="TV Episode 2 (OG)"/>
-    <hyperlink ref="E1529" r:id="rId2036" display="TV Episode 2 (OG)"/>
-    <hyperlink ref="G1529" r:id="rId2037" display="Yoko and Viral can be seen here."/>
-    <hyperlink ref="E1530" r:id="rId2038" display="TV Episode 1"/>
-    <hyperlink ref="E1531" r:id="rId2039" display="TV Episode 2"/>
-    <hyperlink ref="E1532" r:id="rId2040" display="TV Episode 169 (80s)"/>
-    <hyperlink ref="G1532" r:id="rId2041" display="The acquired animation cel and sketch shows in clear details that it is A-ko design"/>
-    <hyperlink ref="E1533" r:id="rId2042" display="TV Episode 11"/>
-    <hyperlink ref="E1534" r:id="rId2043" display="TV Episode 11"/>
-    <hyperlink ref="G1534" r:id="rId2044" display="Danpei can be seen here."/>
-    <hyperlink ref="E1535" r:id="rId2045" display="TV Episode 2 (Shin II)"/>
-    <hyperlink ref="G1535" r:id="rId2046" display="He changes expression here."/>
-    <hyperlink ref="E1536" r:id="rId2047" display="TV Episode 13 (Shin II)"/>
-    <hyperlink ref="E1537" r:id="rId2048" display="TV Episode 153 (OG)"/>
-    <hyperlink ref="G1537" r:id="rId2049" display="Here is the version Toei Europe on Twitter(X) provided."/>
-    <hyperlink ref="E1538" r:id="rId2050" display="TV Episode 23"/>
-    <hyperlink ref="G1538" r:id="rId2051" display="You can see them more clear here."/>
-    <hyperlink ref="E1539" r:id="rId2052" display="TV Episode 36"/>
-    <hyperlink ref="G1539" r:id="rId2053" display="This is reused from episode 23. You can see it more clear here."/>
-    <hyperlink ref="E1540" r:id="rId2054" display="ONA – Hanma Baki vs. Kengan Ashura"/>
-    <hyperlink ref="E1541" r:id="rId2055" display="ONA – Hanma Baki vs. Kengan Ashura"/>
-    <hyperlink ref="E1542" r:id="rId2056" display="TV Episode 247 (Gintama ‘)"/>
-    <hyperlink ref="G1542" r:id="rId2057" display="This is a preview of episode 248"/>
-    <hyperlink ref="E1543" r:id="rId2058" display="TV Episode 248 (Gintama ‘)"/>
-    <hyperlink ref="G1543" r:id="rId2059" display="He can also be seen here and here."/>
-    <hyperlink ref="E1544" r:id="rId2060" display="TV Episode 247 (Gintama ‘)"/>
-    <hyperlink ref="E1545" r:id="rId2061" display="TV Episode 248 (Gintama ‘)"/>
-    <hyperlink ref="E1546" r:id="rId2062" display="TV Episode 53 (80s)"/>
-    <hyperlink ref="E1547" r:id="rId2063" display="TV Episode 26 (Shin)"/>
-    <hyperlink ref="E1548" r:id="rId2064" display="TV Episode 27 (Shin)"/>
-    <hyperlink ref="E1549" r:id="rId2065" display="TV Episode 00"/>
-    <hyperlink ref="E1550" r:id="rId2066" display="TV Episode 51"/>
-    <hyperlink ref="E1551" r:id="rId2067" display="TV Episode 1232"/>
-    <hyperlink ref="E1552" r:id="rId2068" display="TV Episode 1233"/>
-    <hyperlink ref="E1553" r:id="rId2069" display="TV Episode 15 (WP)"/>
-    <hyperlink ref="E1554" r:id="rId2070" display="TV Episode 16 (WP)"/>
-    <hyperlink ref="G1554" r:id="rId2071" display="They appear in the first half of the episode, Shiro even appears at the Home Corner segment of the episode."/>
-    <hyperlink ref="E1555" r:id="rId2072" display="Movie 13 – Wrath of Power"/>
-    <hyperlink ref="E1556" r:id="rId2073" display="TV Episode 43 (20s)"/>
-    <hyperlink ref="E1557" r:id="rId2074" display="TV Episode 46 (20s)"/>
-    <hyperlink ref="E1558" r:id="rId2075" display="TV Episode 142 (80s)"/>
-    <hyperlink ref="E1559" r:id="rId2076" display="TV Episode 142 (80s)"/>
-    <hyperlink ref="E1560" r:id="rId2077" display="TV Episode 1 (OG)"/>
-    <hyperlink ref="G1560" r:id="rId2078" display="The scan from the magazine shows the entire cel which reveals its her. (exact magazine was not found easily, but I suspects its in MissDream)"/>
+    <hyperlink ref="E901" r:id="rId1281" display="TV Episode 73 (Part 2)"/>
+    <hyperlink ref="E902" r:id="rId1282" display="TV Episode 5"/>
+    <hyperlink ref="G902" r:id="rId1283" display="Hikaru can also be seen here."/>
+    <hyperlink ref="E903" r:id="rId1284" display="TV Episode 3"/>
+    <hyperlink ref="E904" r:id="rId1285" display="TV Episode 5"/>
+    <hyperlink ref="E905" r:id="rId1286" display="TV Episode 8"/>
+    <hyperlink ref="E906" r:id="rId1287" display="TV Episode 8"/>
+    <hyperlink ref="E907" r:id="rId1288" display="TV Episode 8 (1991)"/>
+    <hyperlink ref="G907" r:id="rId1289" display="He can also be seen here."/>
+    <hyperlink ref="E908" r:id="rId1290" display="TV Episode 49 (80s)"/>
+    <hyperlink ref="E909" r:id="rId1291" display="TV Episode 13"/>
+    <hyperlink ref="E910" r:id="rId1292" display="TV Episode 13"/>
+    <hyperlink ref="E911" r:id="rId1293" display="TV Episode 13"/>
+    <hyperlink ref="E912" r:id="rId1294" display="TV Episode 13"/>
+    <hyperlink ref="E913" r:id="rId1295" display="TV Episode 15"/>
+    <hyperlink ref="E914" r:id="rId1296" display="TV Episode 10"/>
+    <hyperlink ref="G914" r:id="rId1297" display="Monohoshi Dai can be seen here and Kawa Yui can again be seen here."/>
+    <hyperlink ref="E915" r:id="rId1298" display="TV Episode 10"/>
+    <hyperlink ref="E916" r:id="rId1299" display="TV Episode 110"/>
+    <hyperlink ref="E917" r:id="rId1300" display="TV Episode 5 (1983)"/>
+    <hyperlink ref="E918" r:id="rId1301" display="TV Episode 6 (1983)"/>
+    <hyperlink ref="E919" r:id="rId1302" display="TV Episode 6 (1983)"/>
+    <hyperlink ref="E920" r:id="rId1303" display="TV Episode 6 (1983)"/>
+    <hyperlink ref="E921" r:id="rId1304" display="TV Episode 8 (1983)"/>
+    <hyperlink ref="E922" r:id="rId1305" display="TV Episode 8 (1983)"/>
+    <hyperlink ref="E923" r:id="rId1306" display="TV Episode 111"/>
+    <hyperlink ref="E924" r:id="rId1307" display="TV Episode 118"/>
+    <hyperlink ref="E925" r:id="rId1308" display="TV Episode 23"/>
+    <hyperlink ref="E926" r:id="rId1309" display="TV Episode 23"/>
+    <hyperlink ref="G926" r:id="rId1310" display="You can see them more clear here."/>
+    <hyperlink ref="E927" r:id="rId1311" display="TV Episode 23"/>
+    <hyperlink ref="E928" r:id="rId1312" display="TV Episode 23"/>
+    <hyperlink ref="E929" r:id="rId1313" display="TV Episode 88"/>
+    <hyperlink ref="E930" r:id="rId1314" display="TV Episode 25"/>
+    <hyperlink ref="E931" r:id="rId1315" display="TV Episode 28"/>
+    <hyperlink ref="E932" r:id="rId1316" display="TV Episode 26"/>
+    <hyperlink ref="G932" r:id="rId1317" display="She also can be seen here and here."/>
+    <hyperlink ref="E933" r:id="rId1318" display="TV Episode 26"/>
+    <hyperlink ref="G933" r:id="rId1319" display="She has now a more dark blue hair instead of her usual blond hair. Altough the facial feature, with the hair style and ribbon is still the same. She also can be seen here, here and here."/>
+    <hyperlink ref="E934" r:id="rId1320" display="TV Episode 1"/>
+    <hyperlink ref="E935" r:id="rId1321" display="TV Episode 43 (Part 3)"/>
+    <hyperlink ref="E936" r:id="rId1322" display="TV Episode 98 (80s)"/>
+    <hyperlink ref="G936" r:id="rId1323" display="Yume can be seen here."/>
+    <hyperlink ref="E937" r:id="rId1324" display="TV Episode 39 (Part 3)"/>
+    <hyperlink ref="E938" r:id="rId1325" display="TV Episode 4 (Part 3)"/>
+    <hyperlink ref="G938" r:id="rId1326" display="As the character in the paiting/photograph is sentient, this count as a cameo"/>
+    <hyperlink ref="E939" r:id="rId1327" display="TV Episode 119 (80s)"/>
+    <hyperlink ref="G939" r:id="rId1328" display="A-ko can also be seen here."/>
+    <hyperlink ref="E940" r:id="rId1329" display="TV Episode 119 (80s)"/>
+    <hyperlink ref="E941" r:id="rId1330" display="TV Episode 17"/>
+    <hyperlink ref="E942" r:id="rId1331" display="TV Episode 19"/>
+    <hyperlink ref="E943" r:id="rId1332" display="TV Episode 21"/>
+    <hyperlink ref="G943" r:id="rId1333" display="She can also be seen here."/>
+    <hyperlink ref="E944" r:id="rId1334" display="TV Episode 114 (80s)"/>
+    <hyperlink ref="E945" r:id="rId1335" display="TV Episode 16"/>
+    <hyperlink ref="G945" r:id="rId1336" display="Megane can be seen here"/>
+    <hyperlink ref="E946" r:id="rId1337" display="TV Episode 145 (80s)"/>
+    <hyperlink ref="E947" r:id="rId1338" display="TV Episode 148 (80s)"/>
+    <hyperlink ref="G947" r:id="rId1339" display="Kyao can be seen here and Daiba with Gablae here."/>
+    <hyperlink ref="E948" r:id="rId1340" display="TV Episode 23"/>
+    <hyperlink ref="G948" r:id="rId1341" display="They can also be seen here."/>
+    <hyperlink ref="E949" r:id="rId1342" display="TV Episode 156 (80s)"/>
+    <hyperlink ref="G949" r:id="rId1343" display="This is level 2 as each of the characters move, like here for example. Chilthonia can be seen here."/>
+    <hyperlink ref="E950" r:id="rId1344" display="TV Episode 2"/>
+    <hyperlink ref="E951" r:id="rId1345" display="TV Episode 26"/>
+    <hyperlink ref="G951" r:id="rId1346" display="They can also be seen here."/>
+    <hyperlink ref="E952" r:id="rId1347" display="TV Episode 28"/>
+    <hyperlink ref="G952" r:id="rId1348" display="She can also be seen here, here, here and here."/>
+    <hyperlink ref="E953" r:id="rId1349" display="TV Episode 28"/>
+    <hyperlink ref="G953" r:id="rId1350" display="He can also be seen here"/>
+    <hyperlink ref="E954" r:id="rId1351" display="TV Episode 30"/>
+    <hyperlink ref="E955" r:id="rId1352" display="TV Episode 172 (80s)"/>
+    <hyperlink ref="E956" r:id="rId1353" display="TV Episode 15 (G)"/>
+    <hyperlink ref="G956" r:id="rId1354" display="The reason why this is on level 2 beside the multiple frames is that this boy is part of the plot of this episode"/>
+    <hyperlink ref="E957" r:id="rId1355" display="TV Episode 178 (80s)"/>
+    <hyperlink ref="E958" r:id="rId1356" display="TV Episode 178 (80s)"/>
+    <hyperlink ref="E959" r:id="rId1357" display="TV Episode 176 (80s)"/>
+    <hyperlink ref="E960" r:id="rId1358" display="TV Episode 85"/>
+    <hyperlink ref="G960" r:id="rId1359" display="They moved their eyes in later scenes"/>
+    <hyperlink ref="E961" r:id="rId1360" display="TV Episode 85"/>
+    <hyperlink ref="E962" r:id="rId1361" display="TV Episode 22"/>
+    <hyperlink ref="E963" r:id="rId1362" display="TV Episode 13 (Zeta)"/>
+    <hyperlink ref="E964" r:id="rId1363" display="TV Episode 177 (80s)"/>
+    <hyperlink ref="G964" r:id="rId1364" display="He is eating!"/>
+    <hyperlink ref="E965" r:id="rId1365" display="TV Episode 26"/>
+    <hyperlink ref="E966" r:id="rId1366" display="TV Episode 28"/>
+    <hyperlink ref="E967" r:id="rId1367" display="TV Episode 4"/>
+    <hyperlink ref="G967" r:id="rId1368" display="This, similar to Lum and Ataru in episode 26, Ganmo got edited out in later editions. Ayumi can also be seen here."/>
+    <hyperlink ref="E968" r:id="rId1369" display="Movie 1 - (1986)"/>
+    <hyperlink ref="E969" r:id="rId1370" display="Movie 1 - (1986)"/>
+    <hyperlink ref="E970" r:id="rId1371" display="Movie 1 - (1986)"/>
+    <hyperlink ref="E971" r:id="rId1372" display="Movie 1 - (1986)"/>
+    <hyperlink ref="E972" r:id="rId1373" display="TV Episode 20"/>
+    <hyperlink ref="E973" r:id="rId1374" display="Movie 3 - Remember My Love"/>
+    <hyperlink ref="E974" r:id="rId1375" display="Movie 3 - Remember My Love"/>
+    <hyperlink ref="E975" r:id="rId1376" display="Movie 3 - Remember My Love"/>
+    <hyperlink ref="G975" r:id="rId1377" display="Nurikabe design is specifically unique to the anime/manga show and Kitaro himsef is seen very briefly behind the legs of a women"/>
+    <hyperlink ref="E976" r:id="rId1378" display="Commercial - Partner Agent"/>
+    <hyperlink ref="E977" r:id="rId1379" display="Commercial - Partner Agent"/>
+    <hyperlink ref="E978" r:id="rId1380" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E979" r:id="rId1381" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E980" r:id="rId1382" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E981" r:id="rId1383" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E982" r:id="rId1384" display="TV Special - Black Jack: Karte NG Extras"/>
+    <hyperlink ref="E983" r:id="rId1385" display="Movie 4 - Lum The Forever"/>
+    <hyperlink ref="E984" r:id="rId1386" display="TV Special - Episode 12.5 (2008)"/>
+    <hyperlink ref="E985" r:id="rId1387" display="TV Episode 18"/>
+    <hyperlink ref="E986" r:id="rId1388" display="TV Episode 18"/>
+    <hyperlink ref="E987" r:id="rId1389" display="TV Episode 18"/>
+    <hyperlink ref="E988" r:id="rId1390" display="TV Episode 18"/>
+    <hyperlink ref="E989" r:id="rId1391" display="TV Special - Episode 12.5 (2008)"/>
+    <hyperlink ref="G989" r:id="rId1392" display="Dr. Nambu appears here."/>
+    <hyperlink ref="E990" r:id="rId1393" display="TV Special - Episode 12.5 (2008)"/>
+    <hyperlink ref="E991" r:id="rId1394" display="TV Special - Episode 12.5 (2008)"/>
+    <hyperlink ref="E992" r:id="rId1395" display="OVA - Elf 17"/>
+    <hyperlink ref="E993" r:id="rId1396" display="TV Episode 50 (Grendizer)"/>
+    <hyperlink ref="E994" r:id="rId1397" display="TV Episode 50 (Grendizer)"/>
+    <hyperlink ref="G994" r:id="rId1398" display="Seiji can also be seen here and here."/>
+    <hyperlink ref="E995" r:id="rId1399" display="TV Episode 50 (Grendizer)"/>
+    <hyperlink ref="G995" r:id="rId1400" display="He can also be seen here and here."/>
+    <hyperlink ref="E996" r:id="rId1401" display="TV Episode 3 (80s)"/>
+    <hyperlink ref="E997" r:id="rId1402" display="TV Episode 40"/>
+    <hyperlink ref="G997" r:id="rId1403" display="They are also seen here."/>
+    <hyperlink ref="E998" r:id="rId1404" display="TV Episode 38"/>
+    <hyperlink ref="E999" r:id="rId1405" display="TV Episode 38"/>
+    <hyperlink ref="E1000" r:id="rId1406" display="TV Episode 38"/>
+    <hyperlink ref="E1001" r:id="rId1407" display="TV Episode 38"/>
+    <hyperlink ref="E1002" r:id="rId1408" display="TV Episode 38"/>
+    <hyperlink ref="E1003" r:id="rId1409" display="OVA - (1991)"/>
+    <hyperlink ref="E1004" r:id="rId1410" display="OVA Episode 3 (Shin)"/>
+    <hyperlink ref="E1005" r:id="rId1411" display="OVA Episode 3 (Shin)"/>
+    <hyperlink ref="E1006" r:id="rId1412" display="OVA Episode 3 (Shin)"/>
+    <hyperlink ref="E1007" r:id="rId1413" display="Movie 1 - (1986)"/>
+    <hyperlink ref="E1008" r:id="rId1414" display="OVA Episode 2 (Shin)"/>
+    <hyperlink ref="E1009" r:id="rId1415" display="OVA Episode 2 (Shin)"/>
+    <hyperlink ref="G1009" r:id="rId1416" display="His face gets blowned up."/>
+    <hyperlink ref="E1010" r:id="rId1417" display="OVA Episode 8 (Shin)"/>
+    <hyperlink ref="E1011" r:id="rId1418" display="OVA Episode 8 (Shin)"/>
+    <hyperlink ref="E1012" r:id="rId1419" display="OVA - Elf 17"/>
+    <hyperlink ref="E1013" r:id="rId1420" display="TV Episode 24"/>
+    <hyperlink ref="E1014" r:id="rId1421" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="G1014" r:id="rId1422" display="Kuji can also be seen here and here."/>
+    <hyperlink ref="E1015" r:id="rId1423" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="G1015" r:id="rId1424" display="Ryo Asuka is in his manga design and be seen here and Mikki here."/>
+    <hyperlink ref="E1016" r:id="rId1425" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="G1016" r:id="rId1426" display="She can be seen here and here."/>
+    <hyperlink ref="E1017" r:id="rId1427" display="TV Episode 32"/>
+    <hyperlink ref="E1018" r:id="rId1428" display="TV Episode 21"/>
+    <hyperlink ref="E1019" r:id="rId1429" display="TV Episode 26"/>
+    <hyperlink ref="E1020" r:id="rId1430" display="OVA Episode 8 (Shin)"/>
+    <hyperlink ref="G1020" r:id="rId1431" display="Keiko can be seen here."/>
+    <hyperlink ref="E1021" r:id="rId1432" display="OVA Episode 8 (Shin)"/>
+    <hyperlink ref="E1022" r:id="rId1433" display="OVA Episode 4 (1991)"/>
+    <hyperlink ref="E1023" r:id="rId1434" display="TV Episode 27"/>
+    <hyperlink ref="E1024" r:id="rId1435" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="G1024" r:id="rId1436" display="He can also be seen here."/>
+    <hyperlink ref="E1025" r:id="rId1437" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="E1026" r:id="rId1438" display="OVA Episode 1 (1991)"/>
+    <hyperlink ref="G1026" r:id="rId1439" display="She can also be seen here."/>
+    <hyperlink ref="E1027" r:id="rId1440" display="OVA Episode 4 (1991)"/>
+    <hyperlink ref="G1027" r:id="rId1441" display="She can also be seen here and Alphone here."/>
+    <hyperlink ref="E1028" r:id="rId1442" display="TV Episode 1"/>
+    <hyperlink ref="E1029" r:id="rId1443" display="OVA - (1986)"/>
+    <hyperlink ref="G1029" r:id="rId1444" display="She is chearing"/>
+    <hyperlink ref="E1030" r:id="rId1445" display="OVA - (1986)"/>
+    <hyperlink ref="G1030" r:id="rId1446" display="They are chearing"/>
+    <hyperlink ref="E1031" r:id="rId1447" display="OVA - (1986)"/>
+    <hyperlink ref="G1031" r:id="rId1448" display="She is chearing and Hikaru can be seen here."/>
+    <hyperlink ref="E1032" r:id="rId1449" display="OVA - (1986)"/>
+    <hyperlink ref="G1032" r:id="rId1450" display="He is chearing and can also be seen here."/>
+    <hyperlink ref="E1033" r:id="rId1451" display="OVA - (1986)"/>
+    <hyperlink ref="G1033" r:id="rId1452" display="They are chearing and Gendou Kurosaki can be seen here and here."/>
+    <hyperlink ref="E1034" r:id="rId1453" display="OVA - (1986)"/>
+    <hyperlink ref="G1034" r:id="rId1454" display="They can also be seen here."/>
+    <hyperlink ref="E1035" r:id="rId1455" display="OVA - (1986)"/>
+    <hyperlink ref="G1035" r:id="rId1456" display="He is chearing."/>
+    <hyperlink ref="E1036" r:id="rId1457" display="Movie 3 - Cinderella Rhapsody"/>
+    <hyperlink ref="E1037" r:id="rId1458" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1038" r:id="rId1459" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1039" r:id="rId1460" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1040" r:id="rId1461" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1041" r:id="rId1462" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1042" r:id="rId1463" display="TV Special - Dora・Q・Perman"/>
+    <hyperlink ref="E1043" r:id="rId1464" display="TV Episode 148 (80s)"/>
+    <hyperlink ref="E1044" r:id="rId1465" display="TV Episode 46"/>
+    <hyperlink ref="E1045" r:id="rId1466" display="TV Episode 47"/>
+    <hyperlink ref="E1046" r:id="rId1467" display="Movie 1 - Panda Kopanda"/>
+    <hyperlink ref="G1046" r:id="rId1468" display="They can also be seen here."/>
+    <hyperlink ref="E1047" r:id="rId1469" display="Movie 1 - Panda Kopanda"/>
+    <hyperlink ref="E1048" r:id="rId1470" display="Movie 1 - Panda Kopanda"/>
+    <hyperlink ref="E1049" r:id="rId1471" display="OVA Episode 1 (1989)"/>
+    <hyperlink ref="E1050" r:id="rId1472" display="OVA Episode 2 (1989)"/>
+    <hyperlink ref="G1050" r:id="rId1473" display="This marks his first apperence with a voice, which VA will be used later in the 1991 OVA. He can be seen with Tosaka here."/>
+    <hyperlink ref="E1051" r:id="rId1474" display="Movie 4 - Lum The Forever"/>
+    <hyperlink ref="G1051" r:id="rId1475" display="Ta-Kun can be seen here."/>
+    <hyperlink ref="E1052" r:id="rId1476" display="TV Episode 34 (1966)"/>
+    <hyperlink ref="E1053" r:id="rId1477" display="OVA Episode 1"/>
+    <hyperlink ref="G1053" r:id="rId1478" display="He can also be seen here."/>
+    <hyperlink ref="E1054" r:id="rId1479" display="TV Episode 1"/>
+    <hyperlink ref="G1054" r:id="rId1480" display="Mako can be seen here."/>
+    <hyperlink ref="E1055" r:id="rId1481" display="TV Episode 1"/>
+    <hyperlink ref="E1056" r:id="rId1482" display="TV Episode 2"/>
+    <hyperlink ref="E1057" r:id="rId1483" display="TV Episode 2"/>
+    <hyperlink ref="E1058" r:id="rId1484" display="TV Episode 4"/>
+    <hyperlink ref="E1059" r:id="rId1485" display="TV Episode 6"/>
+    <hyperlink ref="G1059" r:id="rId1486" display="They can also be seen here."/>
+    <hyperlink ref="E1060" r:id="rId1487" display="TV Episode 6"/>
+    <hyperlink ref="E1061" r:id="rId1488" display="TV Episode 6"/>
+    <hyperlink ref="G1061" r:id="rId1489" display="He reacts can be seen here, here, here and here."/>
+    <hyperlink ref="E1062" r:id="rId1490" display="TV Episode 6"/>
+    <hyperlink ref="E1063" r:id="rId1491" display="TV Episode 6"/>
+    <hyperlink ref="E1064" r:id="rId1492" display="TV Episode 6"/>
+    <hyperlink ref="E1065" r:id="rId1493" display="TV Episode 1"/>
+    <hyperlink ref="E1066" r:id="rId1494" display="TV Episode 10"/>
+    <hyperlink ref="G1066" r:id="rId1495" display="He ran away."/>
+    <hyperlink ref="E1067" r:id="rId1496" display="TV Episode 13"/>
+    <hyperlink ref="E1068" r:id="rId1497" display="TV Episode 13"/>
+    <hyperlink ref="E1069" r:id="rId1498" display="TV Episode 13"/>
+    <hyperlink ref="E1070" r:id="rId1499" display="TV Episode 13"/>
+    <hyperlink ref="E1071" r:id="rId1500" display="TV Episode 14"/>
+    <hyperlink ref="G1071" r:id="rId1501" display="He appears here, here and here."/>
+    <hyperlink ref="E1072" r:id="rId1502" display="TV Episode 16"/>
+    <hyperlink ref="E1073" r:id="rId1503" display="TV Episode 21"/>
+    <hyperlink ref="E1074" r:id="rId1504" display="TV Episode 21"/>
+    <hyperlink ref="E1075" r:id="rId1505" display="TV Episode 100 (Part 2)"/>
+    <hyperlink ref="E1076" r:id="rId1506" display="TV Special - Star of the Giants vs. Mighty Atom"/>
+    <hyperlink ref="E1077" r:id="rId1507" display="TV Special - Star of the Giants vs. Mighty Atom"/>
+    <hyperlink ref="E1078" r:id="rId1508" display="TV Episode 21 (OG)"/>
+    <hyperlink ref="E1079" r:id="rId1509" display="Movie - (1983)"/>
+    <hyperlink ref="G1079" r:id="rId1510" display="This has ALOT of Gundam references and cameos. Haro is shown regularly through out the movie, not only that but Char can also seen here up close."/>
+    <hyperlink ref="E1080" r:id="rId1511" display="TV Episode 71 (1983)"/>
+    <hyperlink ref="E1081" r:id="rId1512" display="TV Episode 21 (1983)"/>
+    <hyperlink ref="E1082" r:id="rId1513" display="TV Episode 21 (1983)"/>
+    <hyperlink ref="E1083" r:id="rId1514" display="TV Episode 21 (1983)"/>
+    <hyperlink ref="E1084" r:id="rId1515" display="TV Episode 21 (1983)"/>
+    <hyperlink ref="G1084" r:id="rId1516" display="The untouched Italian version reveals the side brows that confirms its Lupin. Nobuhiro OKASAKO has worked both in Captain Tsubasa and Lupin."/>
+    <hyperlink ref="E1085" r:id="rId1517" display="TV Episode 21 (Season 2)"/>
+    <hyperlink ref="E1086" r:id="rId1518" display="OVA - Devilman: The Birth (1987)"/>
+    <hyperlink ref="E1087" r:id="rId1519" display="TV Episode 50 (Season 2)"/>
+    <hyperlink ref="G1087" r:id="rId1520" display="They look very adult like."/>
+    <hyperlink ref="E1088" r:id="rId1521" display="TV Episode 88 (1980)"/>
+    <hyperlink ref="E1089" r:id="rId1522" display="TV Episode 226 (1980)"/>
+    <hyperlink ref="E1090" r:id="rId1523" display="TV Episode 226 (1980)"/>
+    <hyperlink ref="E1091" r:id="rId1524" display="TV Episode 226 (1980)"/>
+    <hyperlink ref="E1092" r:id="rId1525" display="TV Episode 226 (1980)"/>
+    <hyperlink ref="E1093" r:id="rId1526" display="OVA Episode 2 (Shin)"/>
+    <hyperlink ref="E1094" r:id="rId1527" display="TV Episode 19 (Season 1)"/>
+    <hyperlink ref="E1095" r:id="rId1528" display="TV Episode 19 (Season 1)"/>
+    <hyperlink ref="E1096" r:id="rId1529" display="TV Episode 19 (Season 1)"/>
+    <hyperlink ref="E1097" r:id="rId1530" display="TV Episode 1 (Season 1)"/>
+    <hyperlink ref="G1097" r:id="rId1531" display="She also is seen here and here."/>
+    <hyperlink ref="E1098" r:id="rId1532" display="TV Episode 10 (Season 2)"/>
+    <hyperlink ref="E1099" r:id="rId1533" display="TV Episode 10 (Season 4)"/>
+    <hyperlink ref="G1099" r:id="rId1534" display="Yep, its her alright."/>
+    <hyperlink ref="E1100" r:id="rId1535" display="TV Episode 18"/>
+    <hyperlink ref="G1100" r:id="rId1536" display="As this may be a dream, this still consider as they exists on the same plane. Its also seen here and here."/>
+    <hyperlink ref="E1101" r:id="rId1537" display="TV Episode 18"/>
+    <hyperlink ref="G1101" r:id="rId1538" display="As this may be a dream, this still consider as they exists on the same plane. Its also seen here and here."/>
+    <hyperlink ref="E1102" r:id="rId1539" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1102" r:id="rId1540" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1103" r:id="rId1541" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1103" r:id="rId1542" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1104" r:id="rId1543" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1104" r:id="rId1544" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1105" r:id="rId1545" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1105" r:id="rId1546" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1106" r:id="rId1547" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1106" r:id="rId1548" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1107" r:id="rId1549" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1107" r:id="rId1550" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1108" r:id="rId1551" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1108" r:id="rId1552" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1109" r:id="rId1553" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1109" r:id="rId1554" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1110" r:id="rId1555" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1110" r:id="rId1556" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1111" r:id="rId1557" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1111" r:id="rId1558" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1112" r:id="rId1559" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1112" r:id="rId1560" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1113" r:id="rId1561" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1113" r:id="rId1562" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1114" r:id="rId1563" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1114" r:id="rId1564" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1115" r:id="rId1565" display="Commercial - Mitsukoshi Children's Expo (1986)"/>
+    <hyperlink ref="G1115" r:id="rId1566" display="https://www.youtube.com/watch?v=N3rJ43slik8"/>
+    <hyperlink ref="E1116" r:id="rId1567" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1116" r:id="rId1568" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1117" r:id="rId1569" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1117" r:id="rId1570" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1118" r:id="rId1571" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1118" r:id="rId1572" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1119" r:id="rId1573" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1119" r:id="rId1574" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1120" r:id="rId1575" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1120" r:id="rId1576" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1121" r:id="rId1577" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1121" r:id="rId1578" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1122" r:id="rId1579" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1122" r:id="rId1580" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1123" r:id="rId1581" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1123" r:id="rId1582" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1124" r:id="rId1583" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1124" r:id="rId1584" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1125" r:id="rId1585" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1125" r:id="rId1586" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1126" r:id="rId1587" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1126" r:id="rId1588" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1127" r:id="rId1589" display="Commercial - Hirakata Park The Great Adventure of Goku and Seiya (1988)"/>
+    <hyperlink ref="G1127" r:id="rId1590" display="https://www.youtube.com/watch?v=_NzysgFDI5I"/>
+    <hyperlink ref="E1128" r:id="rId1591" display="TV Episode 2"/>
+    <hyperlink ref="E1129" r:id="rId1592" display="TV Episode 2"/>
+    <hyperlink ref="E1130" r:id="rId1593" display="TV Episode 2"/>
+    <hyperlink ref="E1131" r:id="rId1594" display="Movie 3 - The Legend of the Gold of Babylon"/>
+    <hyperlink ref="E1132" r:id="rId1595" display="Movie 3 - The Legend of the Gold of Babylon"/>
+    <hyperlink ref="E1133" r:id="rId1596" display="TV Episode 1"/>
+    <hyperlink ref="E1134" r:id="rId1597" display="TV Episode 44 (80s)"/>
+    <hyperlink ref="G1134" r:id="rId1598" display="Since the manga was out during this episode premier , Hibaris color is more after the manga appearance. She also is seen here."/>
+    <hyperlink ref="E1135" r:id="rId1599" display="Movie 5 - Dead or Alive"/>
+    <hyperlink ref="E1136" r:id="rId1600" display="Movie 5 - Dead or Alive"/>
+    <hyperlink ref="E1137" r:id="rId1601" display="Movie 5 - Dead or Alive"/>
+    <hyperlink ref="E1138" r:id="rId1602" display="Movie 5 - Dead or Alive"/>
+    <hyperlink ref="E1139" r:id="rId1603" display="Movie 5 - Dead or Alive"/>
+    <hyperlink ref="E1140" r:id="rId1604" display="TV Episode 6 (OG)"/>
+    <hyperlink ref="E1141" r:id="rId1605" display="TV Episode 4"/>
+    <hyperlink ref="G1141" r:id="rId1606" display="The Fossil Creature appears here and here."/>
+    <hyperlink ref="E1142" r:id="rId1607" display="TV Episode 4"/>
+    <hyperlink ref="E1143" r:id="rId1608" display="TV Episode 15"/>
+    <hyperlink ref="E1144" r:id="rId1609" display="TV Episode 15"/>
+    <hyperlink ref="E1145" r:id="rId1610" display="TV Episode 15"/>
+    <hyperlink ref="E1146" r:id="rId1611" display="TV Episode 15"/>
+    <hyperlink ref="G1146" r:id="rId1612" display="Godai can be seen here and here."/>
+    <hyperlink ref="E1147" r:id="rId1613" display="TV Episode 15"/>
+    <hyperlink ref="E1148" r:id="rId1614" display="TV Episode 15"/>
+    <hyperlink ref="E1149" r:id="rId1615" display="TV Episode 16"/>
+    <hyperlink ref="G1149" r:id="rId1616" display="Max and Milia can be seen here and here"/>
+    <hyperlink ref="E1150" r:id="rId1617" display="TV Episode 16"/>
+    <hyperlink ref="G1150" r:id="rId1618" display="She runs."/>
+    <hyperlink ref="E1151" r:id="rId1619" display="TV Episode 16"/>
+    <hyperlink ref="E1152" r:id="rId1620" display="TV Episode 10"/>
+    <hyperlink ref="E1153" r:id="rId1621" display="TV Episode 5"/>
+    <hyperlink ref="G1153" r:id="rId1622" display="They appear constantly in this episode. Boss's little sister can be seen here."/>
+    <hyperlink ref="E1154" r:id="rId1623" display="TV Episode 37"/>
+    <hyperlink ref="E1155" r:id="rId1624" display="TV Episode 2 (Yatterman 2008)"/>
+    <hyperlink ref="E1156" r:id="rId1625" display="TV Episode 7 (Yatterman 2008)"/>
+    <hyperlink ref="E1157" r:id="rId1626" display="TV Episode 24 (Yatterman 2008)"/>
+    <hyperlink ref="G1157" r:id="rId1627" display="Jinpei, Ryu, Ken and Joe can be seen here and they smile."/>
+    <hyperlink ref="E1158" r:id="rId1628" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1159" r:id="rId1629" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1160" r:id="rId1630" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="G1160" r:id="rId1631" display="The car gets trashed later on."/>
+    <hyperlink ref="E1161" r:id="rId1632" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1162" r:id="rId1633" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1163" r:id="rId1634" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1164" r:id="rId1635" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1165" r:id="rId1636" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1166" r:id="rId1637" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1167" r:id="rId1638" display="OVA - Time Bokan: Royal Revival"/>
+    <hyperlink ref="E1168" r:id="rId1639" display="TV Episode 25 (Yatterman 2008)"/>
+    <hyperlink ref="G1168" r:id="rId1640" display="Ryu appears here and here."/>
+    <hyperlink ref="E1169" r:id="rId1641" display="TV Episode 10"/>
+    <hyperlink ref="E1170" r:id="rId1642" display="TV Episode 12"/>
+    <hyperlink ref="E1171" r:id="rId1643" display="TV Episode 13"/>
+    <hyperlink ref="E1172" r:id="rId1644" display="TV Episode 17"/>
+    <hyperlink ref="E1173" r:id="rId1645" display="ONA Episode 5"/>
+    <hyperlink ref="E1174" r:id="rId1646" display="TV Episode 44 (Season 1)"/>
+    <hyperlink ref="E1175" r:id="rId1647" display="TV Episode 5 (Unlimited Psychic Squad)"/>
+    <hyperlink ref="E1176" r:id="rId1648" display="OVA - 2008"/>
+    <hyperlink ref="E1177" r:id="rId1649" display="OVA Episode 2 (Goku)"/>
+    <hyperlink ref="E1178" r:id="rId1650" display="Special - Hetalia = Fantasia"/>
+    <hyperlink ref="E1179" r:id="rId1651" display="Special Event - Anime Tenchou x Touhou Project"/>
+    <hyperlink ref="E1180" r:id="rId1652" display="Special Event - Anime Tenchou x Touhou Project"/>
+    <hyperlink ref="E1181" r:id="rId1653" display="Movie - Lupin III vs. Cat's Eye"/>
+    <hyperlink ref="E1182" r:id="rId1654" display="Movie - Lupin III vs. Cat's Eye"/>
+    <hyperlink ref="E1183" r:id="rId1655" display="TV Episode 13"/>
+    <hyperlink ref="E1184" r:id="rId1656" display="TV Episode 13"/>
+    <hyperlink ref="E1185" r:id="rId1657" display="TV Episode 14"/>
+    <hyperlink ref="E1186" r:id="rId1658" display="TV Episode 14"/>
+    <hyperlink ref="E1187" r:id="rId1659" display="TV Episode 71"/>
+    <hyperlink ref="E1188" r:id="rId1660" display="TV Episode 30"/>
+    <hyperlink ref="E1189" r:id="rId1661" display="TV Episode 3 (Season 2)"/>
+    <hyperlink ref="E1190" r:id="rId1662" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1191" r:id="rId1663" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1192" r:id="rId1664" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1193" r:id="rId1665" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1194" r:id="rId1666" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1195" r:id="rId1667" display="Commercial - Inuyasha Manga Trailer (1996)"/>
+    <hyperlink ref="E1196" r:id="rId1668" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1197" r:id="rId1669" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1198" r:id="rId1670" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1199" r:id="rId1671" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1200" r:id="rId1672" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1201" r:id="rId1673" display="Commercial - Detective Conan Manga Commercial (1995)"/>
+    <hyperlink ref="E1202" r:id="rId1674" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
+    <hyperlink ref="E1203" r:id="rId1675" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
+    <hyperlink ref="E1204" r:id="rId1676" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
+    <hyperlink ref="E1205" r:id="rId1677" display="Commercial - Gambalist! Shun Manga Trailer (1996)"/>
+    <hyperlink ref="E1206" r:id="rId1678" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1207" r:id="rId1679" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1208" r:id="rId1680" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1209" r:id="rId1681" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1210" r:id="rId1682" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1211" r:id="rId1683" display="Commercial - Megumi no Daigo Manga Trailer (1996)"/>
+    <hyperlink ref="E1212" r:id="rId1684" display="Commercial - LOVe Manga Trailer (1996)"/>
+    <hyperlink ref="E1213" r:id="rId1685" display="Commercial - LOVe Manga Trailer (1996)"/>
+    <hyperlink ref="E1214" r:id="rId1686" display="Commercial - LOVe Manga Trailer (1996)"/>
+    <hyperlink ref="E1215" r:id="rId1687" display="Commercial - LOVe Manga Trailer (1996)"/>
+    <hyperlink ref="E1216" r:id="rId1688" display="TV Episode 3"/>
+    <hyperlink ref="E1217" r:id="rId1689" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1218" r:id="rId1690" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1219" r:id="rId1691" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1220" r:id="rId1692" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1221" r:id="rId1693" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1222" r:id="rId1694" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1223" r:id="rId1695" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1224" r:id="rId1696" display="Commercial - Jaja Uma Grooming Up! Manga Commercial (1996)"/>
+    <hyperlink ref="E1225" r:id="rId1697" display="Commercial - H2 Manga Commercial (1996)"/>
+    <hyperlink ref="E1226" r:id="rId1698" display="Commercial - H2 Manga Commercial (1996)"/>
+    <hyperlink ref="E1227" r:id="rId1699" display="Commercial - H2 Manga Commercial (1996)"/>
+    <hyperlink ref="E1228" r:id="rId1700" display="Commercial - H2 Manga Commercial (1996)"/>
+    <hyperlink ref="E1229" r:id="rId1701" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="G1229" r:id="rId1702" display="Genma can be seen here."/>
+    <hyperlink ref="E1230" r:id="rId1703" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="E1231" r:id="rId1704" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="E1232" r:id="rId1705" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="E1233" r:id="rId1706" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="E1234" r:id="rId1707" display="Commercial - Major Manga Commercial (1995)"/>
+    <hyperlink ref="E1235" r:id="rId1708" display="TV Episode 15"/>
+    <hyperlink ref="E1236" r:id="rId1709" display="TV Episode 37"/>
+    <hyperlink ref="G1236" r:id="rId1710" display="They also appear here and here."/>
+    <hyperlink ref="E1237" r:id="rId1711" display="TV Episode 30 (1980)"/>
+    <hyperlink ref="E1238" r:id="rId1712" display="TV Episode 30 (1980)"/>
+    <hyperlink ref="E1239" r:id="rId1713" display="TV Episode 3 (1969)"/>
+    <hyperlink ref="E1240" r:id="rId1714" display="TV Episode 25 (Part 6)"/>
+    <hyperlink ref="E1241" r:id="rId1715" display="TV Episode 25 (Part 6)"/>
+    <hyperlink ref="E1242" r:id="rId1716" display="TV Episode 25 (Part 6)"/>
+    <hyperlink ref="E1243" r:id="rId1717" display="TV Episode 26 (Part 6)"/>
+    <hyperlink ref="G1243" r:id="rId1718" display="Only mentioned through broadcasting channel but does techincally coexist in the world temporarily."/>
+    <hyperlink ref="E1244" r:id="rId1719" display="TV Episode 16"/>
+    <hyperlink ref="E1245" r:id="rId1720" display="TV Episode 22"/>
+    <hyperlink ref="G1245" r:id="rId1721" display="Nobita and the gang can be seen here."/>
+    <hyperlink ref="E1246" r:id="rId1722" display="TV Episode 5 (Lupin Zero)"/>
+    <hyperlink ref="E1247" r:id="rId1723" display="TV Episode 48"/>
+    <hyperlink ref="E1248" r:id="rId1724" display="TV Episode 48"/>
+    <hyperlink ref="E1249" r:id="rId1725" display="TV Episode 49"/>
+    <hyperlink ref="G1249" r:id="rId1726" display="They can be seen here."/>
+    <hyperlink ref="E1250" r:id="rId1727" display="TV Episode 49"/>
+    <hyperlink ref="E1251" r:id="rId1728" display="TV Episode 49"/>
+    <hyperlink ref="E1252" r:id="rId1729" display="TV Episode 49"/>
+    <hyperlink ref="G1252" r:id="rId1730" display="Ittan Mome can be seen here."/>
+    <hyperlink ref="E1253" r:id="rId1731" display="TV Episode 49"/>
+    <hyperlink ref="E1254" r:id="rId1732" display="TV Episode 49"/>
+    <hyperlink ref="G1254" r:id="rId1733" display="He can be seen here and here."/>
+    <hyperlink ref="E1255" r:id="rId1734" display="TV Episode 49"/>
+    <hyperlink ref="E1256" r:id="rId1735" display="TV Episode 49"/>
+    <hyperlink ref="E1257" r:id="rId1736" display="TV Episode 49"/>
+    <hyperlink ref="G1257" r:id="rId1737" display="He can also be seen here."/>
+    <hyperlink ref="E1258" r:id="rId1738" display="Movie - 1970"/>
+    <hyperlink ref="E1259" r:id="rId1739" display="TV Episode 47"/>
+    <hyperlink ref="E1260" r:id="rId1740" display="TV Episode 45"/>
+    <hyperlink ref="G1260" r:id="rId1741" display="He can also be seen here."/>
+    <hyperlink ref="E1261" r:id="rId1742" display="TV Episode 45"/>
+    <hyperlink ref="E1262" r:id="rId1743" display="TV Episode 45"/>
+    <hyperlink ref="E1263" r:id="rId1744" display="TV Episode 44"/>
+    <hyperlink ref="E1264" r:id="rId1745" display="TV Episode 44"/>
+    <hyperlink ref="E1265" r:id="rId1746" display="TV Episode 10"/>
+    <hyperlink ref="E1266" r:id="rId1747" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
+    <hyperlink ref="E1267" r:id="rId1748" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
+    <hyperlink ref="E1268" r:id="rId1749" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
+    <hyperlink ref="E1269" r:id="rId1750" display="Movie - One-Million Year Trip: Bander Book (1978)"/>
+    <hyperlink ref="E1270" r:id="rId1751" display="TV Episode 37"/>
+    <hyperlink ref="E1271" r:id="rId1752" display="TV Episode 37"/>
+    <hyperlink ref="E1272" r:id="rId1753" display="TV Episode 37"/>
+    <hyperlink ref="G1272" r:id="rId1754" display="He can also be seen here."/>
+    <hyperlink ref="E1273" r:id="rId1755" display="TV Episode 37"/>
+    <hyperlink ref="G1273" r:id="rId1756" display="Kogenta Sarutobi can be seen here and here."/>
+    <hyperlink ref="E1274" r:id="rId1757" display="TV Episode 33"/>
+    <hyperlink ref="E1275" r:id="rId1758" display="TV Episode 27"/>
+    <hyperlink ref="G1275" r:id="rId1759" display="Ataru can be seen here. Funny how this is from Hanpeita fantasy as he and Ryuunosuke share the same VA"/>
+    <hyperlink ref="E1276" r:id="rId1760" display="TV Episode 27"/>
+    <hyperlink ref="G1276" r:id="rId1761" display="He can also be seen here."/>
+    <hyperlink ref="E1277" r:id="rId1762" display="TV Episode 27"/>
+    <hyperlink ref="E1278" r:id="rId1763" display="TV Episode 27"/>
+    <hyperlink ref="E1279" r:id="rId1764" display="TV Episode 20"/>
+    <hyperlink ref="G1279" r:id="rId1765" display="Mako can also be seen here."/>
+    <hyperlink ref="E1280" r:id="rId1766" display="TV Episode 20"/>
+    <hyperlink ref="G1280" r:id="rId1767" display="He is also seen here, here, here and here."/>
+    <hyperlink ref="E1281" r:id="rId1768" display="TV Episode 38"/>
+    <hyperlink ref="E1282" r:id="rId1769" display="Movie - Lupin III vs. Cat's Eye"/>
+    <hyperlink ref="E1283" r:id="rId1770" display="Movie - Lupin III vs. Cat's Eye"/>
+    <hyperlink ref="E1284" r:id="rId1771" display="TV Special - Special 3 (OG)"/>
+    <hyperlink ref="E1285" r:id="rId1772" display="TV Episode 1 (OG)"/>
+    <hyperlink ref="E1286" r:id="rId1773" display="Movie - Gu Gu Ganmo (1985)"/>
+    <hyperlink ref="G1286" r:id="rId1774" display="It can also be seen here."/>
+    <hyperlink ref="E1287" r:id="rId1775" display="TV Episode 18"/>
+    <hyperlink ref="E1288" r:id="rId1776" display="Commercial - H2 Manga Commercial (1996)"/>
+    <hyperlink ref="E1289" r:id="rId1777" display="TV Episode 52 (1980)"/>
+    <hyperlink ref="E1290" r:id="rId1778" display="TV Episode 52 (1980)"/>
+    <hyperlink ref="E1291" r:id="rId1779" display="TV Episode 52 (1980)"/>
+    <hyperlink ref="E1292" r:id="rId1780" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1293" r:id="rId1781" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1294" r:id="rId1782" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1295" r:id="rId1783" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1296" r:id="rId1784" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1297" r:id="rId1785" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1298" r:id="rId1786" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1299" r:id="rId1787" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1300" r:id="rId1788" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1301" r:id="rId1789" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1302" r:id="rId1790" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1303" r:id="rId1791" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1304" r:id="rId1792" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1305" r:id="rId1793" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1306" r:id="rId1794" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1307" r:id="rId1795" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1308" r:id="rId1796" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
+    <hyperlink ref="E1309" r:id="rId1797" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
+    <hyperlink ref="E1310" r:id="rId1798" display="Commercial - Karakuri Circus Manga Commercial (1998)"/>
+    <hyperlink ref="E1311" r:id="rId1799" display="TV Episode 35 (Stream)"/>
+    <hyperlink ref="G1311" r:id="rId1800" display="B-ko and C-ko as well"/>
+    <hyperlink ref="E1312" r:id="rId1801" display="TV Episode 3 (OG)"/>
+    <hyperlink ref="E1313" r:id="rId1802" display="TV Episode 137 (80s)"/>
+    <hyperlink ref="G1313" r:id="rId1803" display="They also appears here, here, here, here, here and here."/>
+    <hyperlink ref="E1314" r:id="rId1804" display="TV Episode 137 (80s)"/>
+    <hyperlink ref="G1314" r:id="rId1805" display="They are also seen here."/>
+    <hyperlink ref="E1315" r:id="rId1806" display="TV Episode 22 (20s)"/>
+    <hyperlink ref="E1316" r:id="rId1807" display="TV Episode 158 (80s)"/>
+    <hyperlink ref="E1317" r:id="rId1808" display="TV Episode 3"/>
+    <hyperlink ref="G1317" r:id="rId1809" display="She gasps."/>
+    <hyperlink ref="E1318" r:id="rId1810" display="TV Episode 3"/>
+    <hyperlink ref="E1319" r:id="rId1811" display="TV Episode 8 (1982)"/>
+    <hyperlink ref="E1320" r:id="rId1812" display="TV Episode 5 (1982)"/>
+    <hyperlink ref="E1321" r:id="rId1813" display="TV Episode 2"/>
+    <hyperlink ref="E1322" r:id="rId1814" display="TV Episode 30"/>
+    <hyperlink ref="G1322" r:id="rId1815" display="Arthur Rank can be seen here."/>
+    <hyperlink ref="E1323" r:id="rId1816" display="TV Episode 30"/>
+    <hyperlink ref="E1324" r:id="rId1817" display="TV Episode 30"/>
+    <hyperlink ref="E1325" r:id="rId1818" display="TV Episode 9 (OG)"/>
+    <hyperlink ref="E1326" r:id="rId1819" display="TV Episode 8 (OG)"/>
+    <hyperlink ref="E1327" r:id="rId1820" display="TV Episode 9 (OG)"/>
+    <hyperlink ref="E1328" r:id="rId1821" display="OVA - Farewell My Lovely + Pentagona Dolls"/>
+    <hyperlink ref="E1329" r:id="rId1822" display="TV Episode 13"/>
+    <hyperlink ref="E1330" r:id="rId1823" display="TV Episode 13"/>
+    <hyperlink ref="E1331" r:id="rId1824" display="TV Episode 5"/>
+    <hyperlink ref="E1332" r:id="rId1825" display="TV Episode 50"/>
+    <hyperlink ref="E1333" r:id="rId1826" display="TV Episode 50"/>
+    <hyperlink ref="E1334" r:id="rId1827" display="TV Episode 50"/>
+    <hyperlink ref="E1335" r:id="rId1828" display="TV Episode 50"/>
+    <hyperlink ref="E1336" r:id="rId1829" display="TV Episode 19"/>
+    <hyperlink ref="E1337" r:id="rId1830" display="TV Episode 19"/>
+    <hyperlink ref="E1338" r:id="rId1831" display="TV Episode 19"/>
+    <hyperlink ref="E1339" r:id="rId1832" display="TV Episode 59"/>
+    <hyperlink ref="E1340" r:id="rId1833" display="TV Episode 42"/>
+    <hyperlink ref="E1341" r:id="rId1834" display="TV Episode 59"/>
+    <hyperlink ref="E1342" r:id="rId1835" display="TV Episode 49"/>
+    <hyperlink ref="E1343" r:id="rId1836" display="TV Episode 39 (0079)"/>
+    <hyperlink ref="E1344" r:id="rId1837" display="TV Episode 8"/>
+    <hyperlink ref="E1345" r:id="rId1838" display="TV Episode 8"/>
+    <hyperlink ref="E1346" r:id="rId1839" display="TV Episode 8"/>
+    <hyperlink ref="E1347" r:id="rId1840" display="TV Episode 20 (OG)"/>
+    <hyperlink ref="E1348" r:id="rId1841" display="TV Episode 11"/>
+    <hyperlink ref="E1349" r:id="rId1842" display="TV Episode 11"/>
+    <hyperlink ref="E1350" r:id="rId1843" display="TV Episode 13"/>
+    <hyperlink ref="E1351" r:id="rId1844" display="TV Episode 13"/>
+    <hyperlink ref="E1352" r:id="rId1845" display="TV Episode 13"/>
+    <hyperlink ref="E1353" r:id="rId1846" display="TV Episode 13"/>
+    <hyperlink ref="E1354" r:id="rId1847" display="TV Episode 182"/>
+    <hyperlink ref="E1355" r:id="rId1848" display="TV Episode 26"/>
+    <hyperlink ref="E1356" r:id="rId1849" display="TV Episode 10"/>
+    <hyperlink ref="G1356" r:id="rId1850" display="He is arroused."/>
+    <hyperlink ref="E1357" r:id="rId1851" display="TV Episode 19"/>
+    <hyperlink ref="E1358" r:id="rId1852" display="TV Episode 19"/>
+    <hyperlink ref="E1359" r:id="rId1853" display="TV Episode 19"/>
+    <hyperlink ref="E1360" r:id="rId1854" display="TV Episode 19"/>
+    <hyperlink ref="E1361" r:id="rId1855" display="TV Episode 23"/>
+    <hyperlink ref="G1361" r:id="rId1856" display="He also appears here."/>
+    <hyperlink ref="E1362" r:id="rId1857" display="TV Episode 23"/>
+    <hyperlink ref="E1363" r:id="rId1858" display="TV Episode 23"/>
+    <hyperlink ref="G1363" r:id="rId1859" display="He also appears here thanks to the animation cel and zoomed."/>
+    <hyperlink ref="E1364" r:id="rId1860" display="TV Episode 23"/>
+    <hyperlink ref="E1365" r:id="rId1861" display="TV Episode 19"/>
+    <hyperlink ref="E1366" r:id="rId1862" display="TV Episode 31"/>
+    <hyperlink ref="E1367" r:id="rId1863" display="TV Episode 32"/>
+    <hyperlink ref="G1367" r:id="rId1864" display="She also appears here."/>
+    <hyperlink ref="E1368" r:id="rId1865" display="TV Episode 32"/>
+    <hyperlink ref="G1368" r:id="rId1866" display="She also appears here."/>
+    <hyperlink ref="E1369" r:id="rId1867" display="TV Episode 32"/>
+    <hyperlink ref="G1369" r:id="rId1868" display="She also appears here."/>
+    <hyperlink ref="E1370" r:id="rId1869" display="TV Episode 32"/>
+    <hyperlink ref="E1371" r:id="rId1870" display="TV Episode 36"/>
+    <hyperlink ref="E1372" r:id="rId1871" display="TV Episode 36"/>
+    <hyperlink ref="E1373" r:id="rId1872" display="TV Episode 36"/>
+    <hyperlink ref="E1374" r:id="rId1873" display="TV Episode 36"/>
+    <hyperlink ref="E1375" r:id="rId1874" display="TV Episode 36"/>
+    <hyperlink ref="E1376" r:id="rId1875" display="TV Episode 36"/>
+    <hyperlink ref="G1376" r:id="rId1876" display="This is reused from episode 23. He also appears here thanks to the animation cel and zoomed."/>
+    <hyperlink ref="E1377" r:id="rId1877" display="TV Episode 36"/>
+    <hyperlink ref="E1378" r:id="rId1878" display="TV Episode 36"/>
+    <hyperlink ref="G1378" r:id="rId1879" display="This is reused from episode 23. You can see them more clear here."/>
+    <hyperlink ref="E1379" r:id="rId1880" display="TV Episode 12"/>
+    <hyperlink ref="E1380" r:id="rId1881" display="TV Episode 13"/>
+    <hyperlink ref="E1381" r:id="rId1882" display="TV Episode 15"/>
+    <hyperlink ref="E1382" r:id="rId1883" display="TV Episode 18"/>
+    <hyperlink ref="E1383" r:id="rId1884" display="TV Episode 18"/>
+    <hyperlink ref="E1384" r:id="rId1885" display="TV Episode 18"/>
+    <hyperlink ref="E1385" r:id="rId1886" display="TV Episode 1"/>
+    <hyperlink ref="E1386" r:id="rId1887" display="TV Episode 181 (80s)"/>
+    <hyperlink ref="E1387" r:id="rId1888" display="TV Episode 181 (80s)"/>
+    <hyperlink ref="E1388" r:id="rId1889" display="TV Episode 19"/>
+    <hyperlink ref="E1389" r:id="rId1890" display="TV Episode 3"/>
+    <hyperlink ref="E1390" r:id="rId1891" display="TV Episode 3"/>
+    <hyperlink ref="E1391" r:id="rId1892" display="TV Episode 3"/>
+    <hyperlink ref="E1392" r:id="rId1893" display="TV Episode 4"/>
+    <hyperlink ref="E1393" r:id="rId1894" display="TV Episode 4"/>
+    <hyperlink ref="E1394" r:id="rId1895" display="TV Episode 4"/>
+    <hyperlink ref="E1395" r:id="rId1896" display="TV Episode 4"/>
+    <hyperlink ref="E1396" r:id="rId1897" display="TV Episode 4"/>
+    <hyperlink ref="G1396" r:id="rId1898" display="She also appears here."/>
+    <hyperlink ref="E1397" r:id="rId1899" display="TV Episode 9"/>
+    <hyperlink ref="E1398" r:id="rId1900" display="TV Episode 10"/>
+    <hyperlink ref="E1399" r:id="rId1901" display="TV Episode 10"/>
+    <hyperlink ref="E1400" r:id="rId1902" display="TV Episode 10"/>
+    <hyperlink ref="E1401" r:id="rId1903" display="TV Episode 25 (OG)"/>
+    <hyperlink ref="E1402" r:id="rId1904" display="TV Episode 12"/>
+    <hyperlink ref="E1403" r:id="rId1905" display="TV Episode 12"/>
+    <hyperlink ref="E1404" r:id="rId1906" display="TV Episode 21 (Z)"/>
+    <hyperlink ref="E1405" r:id="rId1907" display="TV Episode 20 (Z)"/>
+    <hyperlink ref="E1406" r:id="rId1908" display="TV Episode 30 (OG)"/>
+    <hyperlink ref="E1407" r:id="rId1909" display="TV Episode 86 (OG)"/>
+    <hyperlink ref="E1408" r:id="rId1910" display="TV Episode 107 (OG)"/>
+    <hyperlink ref="E1409" r:id="rId1911" display="TV Episode 109 (OG)"/>
+    <hyperlink ref="E1410" r:id="rId1912" display="TV Episode 14"/>
+    <hyperlink ref="E1411" r:id="rId1913" display="TV Episode 14"/>
+    <hyperlink ref="E1412" r:id="rId1914" display="TV Episode 16"/>
+    <hyperlink ref="E1413" r:id="rId1915" display="TV Episode 18"/>
+    <hyperlink ref="E1414" r:id="rId1916" display="Movie - Angel Dust"/>
+    <hyperlink ref="E1415" r:id="rId1917" display="TV Episode 9"/>
+    <hyperlink ref="E1416" r:id="rId1918" display="Special - Tokyo Crisis"/>
+    <hyperlink ref="E1417" r:id="rId1919" display="Movie - Ribbon no Kishi"/>
+    <hyperlink ref="E1418" r:id="rId1920" display="Movie - Ribbon no Kishi"/>
+    <hyperlink ref="E1419" r:id="rId1921" display="TV Episode 1"/>
+    <hyperlink ref="E1420" r:id="rId1922" display="TV Episode 14 (OG)"/>
+    <hyperlink ref="G1420" r:id="rId1923" display="She gets blown away."/>
+    <hyperlink ref="E1421" r:id="rId1924" display="TV Episode 15 (OG)"/>
+    <hyperlink ref="E1422" r:id="rId1925" display="TV Episode 15 (OG)"/>
+    <hyperlink ref="E1423" r:id="rId1926" display="TV Episode 15 (OG)"/>
+    <hyperlink ref="E1424" r:id="rId1927" display="TV Episode 23 (OG)"/>
+    <hyperlink ref="E1425" r:id="rId1928" display="TV Episode 18 (OG)"/>
+    <hyperlink ref="E1426" r:id="rId1929" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="E1427" r:id="rId1930" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="G1427" r:id="rId1931" display="Kate can also be seen here, Barts here and Luchina here."/>
+    <hyperlink ref="E1428" r:id="rId1932" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="E1429" r:id="rId1933" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="E1430" r:id="rId1934" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="E1431" r:id="rId1935" display="TV Episode 26 (OG)"/>
+    <hyperlink ref="E1432" r:id="rId1936" display="TV Episode 23 (OG)"/>
+    <hyperlink ref="E1433" r:id="rId1937" display="Movie 4 - Lum The Forever"/>
+    <hyperlink ref="E1434" r:id="rId1938" display="TV Episode 31 (OG)"/>
+    <hyperlink ref="E1435" r:id="rId1939" display="TV Episode 34 (OG)"/>
+    <hyperlink ref="G1435" r:id="rId1940" display="It can also be seen here and here."/>
+    <hyperlink ref="E1436" r:id="rId1941" display="TV Episode 34 (OG)"/>
+    <hyperlink ref="E1437" r:id="rId1942" display="TV Episode 35 (OG)"/>
+    <hyperlink ref="G1437" r:id="rId1943" display="It can also be seen here."/>
+    <hyperlink ref="E1438" r:id="rId1944" display="TV Episode 35 (OG)"/>
+    <hyperlink ref="E1439" r:id="rId1945" display="OVA Episode 2"/>
+    <hyperlink ref="E1440" r:id="rId1946" display="TV Episode 34 (OG)"/>
+    <hyperlink ref="E1441" r:id="rId1947" display="OVA Episode 5 (Macross II)"/>
+    <hyperlink ref="E1442" r:id="rId1948" display="Movie - Black Jack: Dr. Pinoko's Adventure"/>
+    <hyperlink ref="E1443" r:id="rId1949" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1444" r:id="rId1950" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1445" r:id="rId1951" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1446" r:id="rId1952" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1447" r:id="rId1953" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1448" r:id="rId1954" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1449" r:id="rId1955" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1450" r:id="rId1956" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1451" r:id="rId1957" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1452" r:id="rId1958" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1453" r:id="rId1959" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1454" r:id="rId1960" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1455" r:id="rId1961" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1456" r:id="rId1962" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1457" r:id="rId1963" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1458" r:id="rId1964" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1459" r:id="rId1965" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1460" r:id="rId1966" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1461" r:id="rId1967" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1462" r:id="rId1968" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1463" r:id="rId1969" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1464" r:id="rId1970" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1465" r:id="rId1971" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1466" r:id="rId1972" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1467" r:id="rId1973" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1468" r:id="rId1974" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1469" r:id="rId1975" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1470" r:id="rId1976" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1471" r:id="rId1977" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1472" r:id="rId1978" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1473" r:id="rId1979" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1474" r:id="rId1980" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1475" r:id="rId1981" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1476" r:id="rId1982" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1477" r:id="rId1983" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1478" r:id="rId1984" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1479" r:id="rId1985" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1480" r:id="rId1986" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1481" r:id="rId1987" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1482" r:id="rId1988" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1483" r:id="rId1989" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1484" r:id="rId1990" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1485" r:id="rId1991" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1486" r:id="rId1992" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1487" r:id="rId1993" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1488" r:id="rId1994" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1489" r:id="rId1995" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1490" r:id="rId1996" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1491" r:id="rId1997" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1492" r:id="rId1998" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1493" r:id="rId1999" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1494" r:id="rId2000" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1495" r:id="rId2001" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1496" r:id="rId2002" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1497" r:id="rId2003" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1498" r:id="rId2004" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1499" r:id="rId2005" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1500" r:id="rId2006" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1501" r:id="rId2007" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1502" r:id="rId2008" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1503" r:id="rId2009" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1504" r:id="rId2010" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1505" r:id="rId2011" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1506" r:id="rId2012" display="OVA - Ravex in Tezuka World"/>
+    <hyperlink ref="E1507" r:id="rId2013" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1508" r:id="rId2014" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1509" r:id="rId2015" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1510" r:id="rId2016" display="TV Special - Last Miracle 20th Century"/>
+    <hyperlink ref="E1511" r:id="rId2017" display="OVA Episode 3 (Mobile Suit SD Gundam)"/>
+    <hyperlink ref="E1512" r:id="rId2018" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1513" r:id="rId2019" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1514" r:id="rId2020" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1515" r:id="rId2021" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1516" r:id="rId2022" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1517" r:id="rId2023" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1518" r:id="rId2024" display="Movie - Choro-Q Dougram"/>
+    <hyperlink ref="E1519" r:id="rId2025" display="TV Episode 18 (Zeta)"/>
+    <hyperlink ref="E1520" r:id="rId2026" display="Movie - (1983)"/>
+    <hyperlink ref="E1521" r:id="rId2027" display="ONA - Genjitsu no Rimuru: Sunshine in the Slime"/>
+    <hyperlink ref="E1522" r:id="rId2028" display="ONA - Genjitsu no Rimuru: Sunshine in the Slime"/>
+    <hyperlink ref="E1523" r:id="rId2029" display="TV Episode 3 (OG)"/>
+    <hyperlink ref="E1524" r:id="rId2030" display="TV Episode 11 (OG)"/>
+    <hyperlink ref="G1524" r:id="rId2031" display="She also appears here."/>
+    <hyperlink ref="E1525" r:id="rId2032" display="TV Episode 12 (OG)"/>
+    <hyperlink ref="G1525" r:id="rId2033" display="They can also be seen here."/>
+    <hyperlink ref="E1526" r:id="rId2034" display="TV Episode 16 (OG)"/>
+    <hyperlink ref="E1527" r:id="rId2035" display="TV Episode 21 (OG)"/>
+    <hyperlink ref="E1528" r:id="rId2036" display="TV Episode 2 (OG)"/>
+    <hyperlink ref="E1529" r:id="rId2037" display="TV Episode 2 (OG)"/>
+    <hyperlink ref="G1529" r:id="rId2038" display="Yoko and Viral can be seen here."/>
+    <hyperlink ref="E1530" r:id="rId2039" display="TV Episode 1"/>
+    <hyperlink ref="E1531" r:id="rId2040" display="TV Episode 2"/>
+    <hyperlink ref="E1532" r:id="rId2041" display="TV Episode 169 (80s)"/>
+    <hyperlink ref="G1532" r:id="rId2042" display="The acquired animation cel and sketch shows in clear details that it is A-ko design"/>
+    <hyperlink ref="E1533" r:id="rId2043" display="TV Episode 11"/>
+    <hyperlink ref="E1534" r:id="rId2044" display="TV Episode 11"/>
+    <hyperlink ref="G1534" r:id="rId2045" display="Danpei can be seen here."/>
+    <hyperlink ref="E1535" r:id="rId2046" display="TV Episode 2 (Shin II)"/>
+    <hyperlink ref="G1535" r:id="rId2047" display="He changes expression here."/>
+    <hyperlink ref="E1536" r:id="rId2048" display="TV Episode 13 (Shin II)"/>
+    <hyperlink ref="E1537" r:id="rId2049" display="TV Episode 153 (OG)"/>
+    <hyperlink ref="G1537" r:id="rId2050" display="Here is the version Toei Europe on Twitter(X) provided."/>
+    <hyperlink ref="E1538" r:id="rId2051" display="TV Episode 23"/>
+    <hyperlink ref="G1538" r:id="rId2052" display="You can see them more clear here."/>
+    <hyperlink ref="E1539" r:id="rId2053" display="TV Episode 36"/>
+    <hyperlink ref="G1539" r:id="rId2054" display="This is reused from episode 23. You can see it more clear here."/>
+    <hyperlink ref="E1540" r:id="rId2055" display="ONA – Hanma Baki vs. Kengan Ashura"/>
+    <hyperlink ref="E1541" r:id="rId2056" display="ONA – Hanma Baki vs. Kengan Ashura"/>
+    <hyperlink ref="E1542" r:id="rId2057" display="TV Episode 247 (Gintama ‘)"/>
+    <hyperlink ref="G1542" r:id="rId2058" display="This is a preview of episode 248"/>
+    <hyperlink ref="E1543" r:id="rId2059" display="TV Episode 248 (Gintama ‘)"/>
+    <hyperlink ref="G1543" r:id="rId2060" display="He can also be seen here and here."/>
+    <hyperlink ref="E1544" r:id="rId2061" display="TV Episode 247 (Gintama ‘)"/>
+    <hyperlink ref="E1545" r:id="rId2062" display="TV Episode 248 (Gintama ‘)"/>
+    <hyperlink ref="E1546" r:id="rId2063" display="TV Episode 53 (80s)"/>
+    <hyperlink ref="E1547" r:id="rId2064" display="TV Episode 26 (Shin)"/>
+    <hyperlink ref="E1548" r:id="rId2065" display="TV Episode 27 (Shin)"/>
+    <hyperlink ref="E1549" r:id="rId2066" display="TV Episode 00"/>
+    <hyperlink ref="E1550" r:id="rId2067" display="TV Episode 51"/>
+    <hyperlink ref="E1551" r:id="rId2068" display="TV Episode 1232"/>
+    <hyperlink ref="E1552" r:id="rId2069" display="TV Episode 1233"/>
+    <hyperlink ref="E1553" r:id="rId2070" display="TV Episode 15 (WP)"/>
+    <hyperlink ref="E1554" r:id="rId2071" display="TV Episode 16 (WP)"/>
+    <hyperlink ref="G1554" r:id="rId2072" display="They appear in the first half of the episode, Shiro even appears at the Home Corner segment of the episode."/>
+    <hyperlink ref="E1555" r:id="rId2073" display="Movie 13 – Wrath of Power"/>
+    <hyperlink ref="E1556" r:id="rId2074" display="TV Episode 43 (20s)"/>
+    <hyperlink ref="E1557" r:id="rId2075" display="TV Episode 46 (20s)"/>
+    <hyperlink ref="E1558" r:id="rId2076" display="TV Episode 142 (80s)"/>
+    <hyperlink ref="E1559" r:id="rId2077" display="TV Episode 142 (80s)"/>
+    <hyperlink ref="E1560" r:id="rId2078" display="TV Episode 1 (OG)"/>
+    <hyperlink ref="G1560" r:id="rId2079" display="The scan from the magazine shows the entire cel which reveals its her. (exact magazine was not found easily, but I suspects its in MissDream)"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -49188,8 +49189,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2079"/>
-  <legacyDrawing r:id="rId2080"/>
+  <drawing r:id="rId2080"/>
+  <legacyDrawing r:id="rId2081"/>
 </worksheet>
 </file>
 

--- a/xlsxFiles/Crossover_Cameos_in_Anime_Evidence_List_Only.xlsx
+++ b/xlsxFiles/Crossover_Cameos_in_Anime_Evidence_List_Only.xlsx
@@ -5611,9 +5611,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2827800</xdr:colOff>
+      <xdr:colOff>2827440</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>132840</xdr:rowOff>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5627,7 +5627,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="19506600" cy="12772440"/>
+          <a:ext cx="19506960" cy="12772080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5829,7 +5829,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="43.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.75"/>
   </cols>
